--- a/aspirantura_kalkulyator.xlsx
+++ b/aspirantura_kalkulyator.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -160,8 +160,11 @@
       <color rgb="FF0563C1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -190,6 +193,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -227,7 +235,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -451,6 +459,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -983,14 +992,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>УВАГА, КАНДИДАТ 2. Пріоритет — НУ «Запорізька політехніка», «Електронна інженерія». Це галузь «Інженерія, виробництво та будівництво», а НЕ «Інформаційні технології»: аркуш «Розрахунок по ЗВО» покриває лише F1-F7 і цієї пропозиції не містить. Квота держзамовлення на IT (769 місць) до неї теж не стосується — електроніка фінансується з іншої галузевої квоти.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Ваги випробувань у «Електронній інженерії» майже напевно інші, ніж у F3. Поки пропозицію не вивантажено зі «Вступ.ОСВІТА.UA», КБ по ній не рахується.</t>
         </is>
@@ -1009,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AI120"/>
+  <dimension ref="A1:AN120"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="37" min="1" max="1"/>
@@ -1043,6 +1052,11 @@
     <col width="16" customWidth="1" style="37" min="33" max="33"/>
     <col width="13" customWidth="1" style="37" min="34" max="34"/>
     <col width="16" customWidth="1" style="37" min="35" max="35"/>
+    <col width="14" customWidth="1" style="38" min="36" max="36"/>
+    <col width="16" customWidth="1" style="38" min="37" max="37"/>
+    <col width="14" customWidth="1" style="38" min="38" max="38"/>
+    <col width="22" customWidth="1" style="38" min="39" max="39"/>
+    <col width="22" customWidth="1" style="38" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="39.75" customHeight="1" s="38">
@@ -1221,6 +1235,31 @@
           <t>Запит/відповідь</t>
         </is>
       </c>
+      <c r="AJ1" s="75" t="inlineStr">
+        <is>
+          <t>Мін. бал ЄВВ</t>
+        </is>
+      </c>
+      <c r="AK1" s="75" t="inlineStr">
+        <is>
+          <t>Мін. бал іноземної</t>
+        </is>
+      </c>
+      <c r="AL1" s="75" t="inlineStr">
+        <is>
+          <t>Мін. бал ТЗНК</t>
+        </is>
+      </c>
+      <c r="AM1" s="75" t="inlineStr">
+        <is>
+          <t>Допуск ЄВВ К1</t>
+        </is>
+      </c>
+      <c r="AN1" s="75" t="inlineStr">
+        <is>
+          <t>Допуск ЄВВ К2</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="38">
       <c r="A2" s="51" t="inlineStr">
@@ -1349,6 +1388,17 @@
       <c r="AG2" s="60" t="n"/>
       <c r="AH2" s="60" t="n"/>
       <c r="AI2" s="52" t="n"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2">
+        <f>IF(AJ2="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ2,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN2">
+        <f>IF(AJ2="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ2,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="3" ht="26.85" customHeight="1" s="38">
       <c r="A3" s="51" t="inlineStr">
@@ -1477,6 +1527,17 @@
       <c r="AG3" s="60" t="n"/>
       <c r="AH3" s="60" t="n"/>
       <c r="AI3" s="52" t="n"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3">
+        <f>IF(AJ3="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ3,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN3">
+        <f>IF(AJ3="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ3,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="4" ht="26.85" customHeight="1" s="38">
       <c r="A4" s="51" t="inlineStr">
@@ -1631,6 +1692,17 @@
       <c r="AG4" s="60" t="n"/>
       <c r="AH4" s="60" t="n"/>
       <c r="AI4" s="52" t="n"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4">
+        <f>IF(AJ4="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ4,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN4">
+        <f>IF(AJ4="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ4,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="5" ht="26.85" customHeight="1" s="38">
       <c r="A5" s="51" t="inlineStr">
@@ -1755,6 +1827,17 @@
       <c r="AG5" s="60" t="n"/>
       <c r="AH5" s="60" t="n"/>
       <c r="AI5" s="52" t="n"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5">
+        <f>IF(AJ5="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ5,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN5">
+        <f>IF(AJ5="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ5,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="38">
       <c r="A6" s="51" t="inlineStr">
@@ -1883,6 +1966,17 @@
       <c r="AG6" s="60" t="n"/>
       <c r="AH6" s="60" t="n"/>
       <c r="AI6" s="52" t="n"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6">
+        <f>IF(AJ6="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ6,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN6">
+        <f>IF(AJ6="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ6,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="38">
       <c r="A7" s="51" t="inlineStr">
@@ -2007,6 +2101,17 @@
       <c r="AG7" s="60" t="n"/>
       <c r="AH7" s="60" t="n"/>
       <c r="AI7" s="52" t="n"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7">
+        <f>IF(AJ7="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ7,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN7">
+        <f>IF(AJ7="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ7,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="26.85" customHeight="1" s="38">
       <c r="A8" s="51" t="inlineStr">
@@ -2131,6 +2236,17 @@
       <c r="AG8" s="60" t="n"/>
       <c r="AH8" s="60" t="n"/>
       <c r="AI8" s="52" t="n"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8">
+        <f>IF(AJ8="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ8,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN8">
+        <f>IF(AJ8="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ8,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="38">
       <c r="A9" s="51" t="inlineStr">
@@ -2263,6 +2379,17 @@
       <c r="AG9" s="60" t="n"/>
       <c r="AH9" s="60" t="n"/>
       <c r="AI9" s="52" t="n"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9">
+        <f>IF(AJ9="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ9,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN9">
+        <f>IF(AJ9="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ9,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="38">
       <c r="A10" s="51" t="inlineStr">
@@ -2389,6 +2516,17 @@
       <c r="AG10" s="60" t="n"/>
       <c r="AH10" s="60" t="n"/>
       <c r="AI10" s="52" t="n"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10">
+        <f>IF(AJ10="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ10,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN10">
+        <f>IF(AJ10="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ10,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="38">
       <c r="A11" s="51" t="inlineStr">
@@ -2531,6 +2669,17 @@
       <c r="AG11" s="60" t="n"/>
       <c r="AH11" s="60" t="n"/>
       <c r="AI11" s="52" t="n"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11">
+        <f>IF(AJ11="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ11,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN11">
+        <f>IF(AJ11="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ11,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="26.85" customHeight="1" s="38">
       <c r="A12" s="51" t="inlineStr">
@@ -2659,6 +2808,17 @@
       <c r="AG12" s="60" t="n"/>
       <c r="AH12" s="60" t="n"/>
       <c r="AI12" s="52" t="n"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12">
+        <f>IF(AJ12="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ12,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN12">
+        <f>IF(AJ12="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ12,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="38">
       <c r="A13" s="51" t="inlineStr">
@@ -2791,6 +2951,17 @@
       <c r="AG13" s="60" t="n"/>
       <c r="AH13" s="60" t="n"/>
       <c r="AI13" s="52" t="n"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13">
+        <f>IF(AJ13="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ13,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN13">
+        <f>IF(AJ13="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ13,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="38">
       <c r="A14" s="51" t="inlineStr">
@@ -2919,6 +3090,17 @@
       <c r="AG14" s="60" t="n"/>
       <c r="AH14" s="60" t="n"/>
       <c r="AI14" s="52" t="n"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14">
+        <f>IF(AJ14="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ14,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN14">
+        <f>IF(AJ14="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ14,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="38">
       <c r="A15" s="51" t="inlineStr">
@@ -3051,6 +3233,17 @@
       <c r="AG15" s="60" t="n"/>
       <c r="AH15" s="60" t="n"/>
       <c r="AI15" s="52" t="n"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15">
+        <f>IF(AJ15="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ15,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN15">
+        <f>IF(AJ15="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ15,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="38">
       <c r="A16" s="51" t="inlineStr">
@@ -3177,6 +3370,17 @@
       <c r="AG16" s="60" t="n"/>
       <c r="AH16" s="60" t="n"/>
       <c r="AI16" s="52" t="n"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16">
+        <f>IF(AJ16="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ16,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN16">
+        <f>IF(AJ16="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ16,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="38">
       <c r="A17" s="51" t="inlineStr">
@@ -3309,6 +3513,17 @@
       <c r="AG17" s="60" t="n"/>
       <c r="AH17" s="60" t="n"/>
       <c r="AI17" s="52" t="n"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17">
+        <f>IF(AJ17="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ17,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN17">
+        <f>IF(AJ17="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ17,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="38">
       <c r="A18" s="51" t="inlineStr">
@@ -3443,6 +3658,17 @@
       <c r="AG18" s="60" t="n"/>
       <c r="AH18" s="60" t="n"/>
       <c r="AI18" s="52" t="n"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18">
+        <f>IF(AJ18="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ18,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN18">
+        <f>IF(AJ18="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ18,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="38">
       <c r="A19" s="51" t="inlineStr">
@@ -3567,6 +3793,17 @@
       <c r="AG19" s="60" t="n"/>
       <c r="AH19" s="60" t="n"/>
       <c r="AI19" s="52" t="n"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19">
+        <f>IF(AJ19="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ19,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN19">
+        <f>IF(AJ19="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ19,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="38">
       <c r="A20" s="51" t="inlineStr">
@@ -3691,6 +3928,17 @@
       <c r="AG20" s="60" t="n"/>
       <c r="AH20" s="60" t="n"/>
       <c r="AI20" s="52" t="n"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20">
+        <f>IF(AJ20="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ20,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN20">
+        <f>IF(AJ20="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ20,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="38">
       <c r="A21" s="51" t="inlineStr">
@@ -3817,6 +4065,17 @@
       <c r="AG21" s="60" t="n"/>
       <c r="AH21" s="60" t="n"/>
       <c r="AI21" s="52" t="n"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21">
+        <f>IF(AJ21="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ21,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN21">
+        <f>IF(AJ21="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ21,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="26.85" customHeight="1" s="38">
       <c r="A22" s="51" t="inlineStr">
@@ -3959,6 +4218,17 @@
       <c r="AG22" s="60" t="n"/>
       <c r="AH22" s="60" t="n"/>
       <c r="AI22" s="52" t="n"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22">
+        <f>IF(AJ22="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ22,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN22">
+        <f>IF(AJ22="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ22,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="38">
       <c r="A23" s="51" t="inlineStr">
@@ -4087,6 +4357,17 @@
       <c r="AG23" s="60" t="n"/>
       <c r="AH23" s="60" t="n"/>
       <c r="AI23" s="52" t="n"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23">
+        <f>IF(AJ23="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ23,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN23">
+        <f>IF(AJ23="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ23,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="38">
       <c r="A24" s="51" t="inlineStr">
@@ -4209,6 +4490,17 @@
       <c r="AG24" s="60" t="n"/>
       <c r="AH24" s="60" t="n"/>
       <c r="AI24" s="52" t="n"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24">
+        <f>IF(AJ24="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ24,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN24">
+        <f>IF(AJ24="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ24,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="38">
       <c r="A25" s="51" t="inlineStr">
@@ -4341,6 +4633,17 @@
       <c r="AG25" s="60" t="n"/>
       <c r="AH25" s="60" t="n"/>
       <c r="AI25" s="52" t="n"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25">
+        <f>IF(AJ25="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ25,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN25">
+        <f>IF(AJ25="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ25,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="38">
       <c r="A26" s="51" t="inlineStr">
@@ -4469,6 +4772,17 @@
       <c r="AG26" s="60" t="n"/>
       <c r="AH26" s="60" t="n"/>
       <c r="AI26" s="52" t="n"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26">
+        <f>IF(AJ26="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ26,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN26">
+        <f>IF(AJ26="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ26,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="38">
       <c r="A27" s="51" t="inlineStr">
@@ -4595,6 +4909,17 @@
       <c r="AG27" s="60" t="n"/>
       <c r="AH27" s="60" t="n"/>
       <c r="AI27" s="52" t="n"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27">
+        <f>IF(AJ27="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ27,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN27">
+        <f>IF(AJ27="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ27,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="38">
       <c r="A28" s="51" t="inlineStr">
@@ -4719,6 +5044,17 @@
       <c r="AG28" s="60" t="n"/>
       <c r="AH28" s="60" t="n"/>
       <c r="AI28" s="52" t="n"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28">
+        <f>IF(AJ28="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ28,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN28">
+        <f>IF(AJ28="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ28,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="26.85" customHeight="1" s="38">
       <c r="A29" s="51" t="inlineStr">
@@ -4861,6 +5197,17 @@
       <c r="AG29" s="60" t="n"/>
       <c r="AH29" s="60" t="n"/>
       <c r="AI29" s="52" t="n"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29">
+        <f>IF(AJ29="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ29,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN29">
+        <f>IF(AJ29="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ29,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="38">
       <c r="A30" s="51" t="inlineStr">
@@ -4991,6 +5338,17 @@
       <c r="AG30" s="60" t="n"/>
       <c r="AH30" s="60" t="n"/>
       <c r="AI30" s="52" t="n"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30">
+        <f>IF(AJ30="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ30,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN30">
+        <f>IF(AJ30="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ30,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="38">
       <c r="A31" s="51" t="inlineStr">
@@ -5119,6 +5477,17 @@
       <c r="AG31" s="60" t="n"/>
       <c r="AH31" s="60" t="n"/>
       <c r="AI31" s="52" t="n"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31">
+        <f>IF(AJ31="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ31,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN31">
+        <f>IF(AJ31="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ31,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="38">
       <c r="A32" s="51" t="inlineStr">
@@ -5241,6 +5610,17 @@
       <c r="AG32" s="60" t="n"/>
       <c r="AH32" s="60" t="n"/>
       <c r="AI32" s="52" t="n"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32">
+        <f>IF(AJ32="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ32,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN32">
+        <f>IF(AJ32="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ32,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="38">
       <c r="A33" s="51" t="inlineStr">
@@ -5369,6 +5749,17 @@
       <c r="AG33" s="60" t="n"/>
       <c r="AH33" s="60" t="n"/>
       <c r="AI33" s="52" t="n"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33">
+        <f>IF(AJ33="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ33,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN33">
+        <f>IF(AJ33="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ33,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="26.85" customHeight="1" s="38">
       <c r="A34" s="51" t="inlineStr">
@@ -5511,6 +5902,17 @@
       <c r="AG34" s="60" t="n"/>
       <c r="AH34" s="60" t="n"/>
       <c r="AI34" s="52" t="n"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34">
+        <f>IF(AJ34="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ34,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN34">
+        <f>IF(AJ34="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ34,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="38">
       <c r="A35" s="51" t="inlineStr">
@@ -5635,6 +6037,17 @@
       <c r="AG35" s="60" t="n"/>
       <c r="AH35" s="60" t="n"/>
       <c r="AI35" s="52" t="n"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35">
+        <f>IF(AJ35="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ35,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN35">
+        <f>IF(AJ35="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ35,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="38">
       <c r="A36" s="51" t="inlineStr">
@@ -5765,6 +6178,17 @@
       <c r="AG36" s="60" t="n"/>
       <c r="AH36" s="60" t="n"/>
       <c r="AI36" s="52" t="n"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36">
+        <f>IF(AJ36="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ36,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN36">
+        <f>IF(AJ36="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ36,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="38">
       <c r="A37" s="51" t="inlineStr">
@@ -5889,6 +6313,17 @@
       <c r="AG37" s="60" t="n"/>
       <c r="AH37" s="60" t="n"/>
       <c r="AI37" s="52" t="n"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37">
+        <f>IF(AJ37="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ37,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN37">
+        <f>IF(AJ37="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ37,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="26.85" customHeight="1" s="38">
       <c r="A38" s="51" t="inlineStr">
@@ -6013,6 +6448,17 @@
       <c r="AG38" s="60" t="n"/>
       <c r="AH38" s="60" t="n"/>
       <c r="AI38" s="52" t="n"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38">
+        <f>IF(AJ38="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ38,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN38">
+        <f>IF(AJ38="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ38,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="38">
       <c r="A39" s="51" t="inlineStr">
@@ -6143,6 +6589,17 @@
       <c r="AG39" s="60" t="n"/>
       <c r="AH39" s="60" t="n"/>
       <c r="AI39" s="52" t="n"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39">
+        <f>IF(AJ39="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ39,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN39">
+        <f>IF(AJ39="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ39,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="26.85" customHeight="1" s="38">
       <c r="A40" s="51" t="inlineStr">
@@ -6285,6 +6742,17 @@
       <c r="AG40" s="60" t="n"/>
       <c r="AH40" s="60" t="n"/>
       <c r="AI40" s="52" t="n"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40">
+        <f>IF(AJ40="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ40,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN40">
+        <f>IF(AJ40="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ40,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="38">
       <c r="A41" s="51" t="inlineStr">
@@ -6411,6 +6879,17 @@
       <c r="AG41" s="60" t="n"/>
       <c r="AH41" s="60" t="n"/>
       <c r="AI41" s="52" t="n"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41">
+        <f>IF(AJ41="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ41,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN41">
+        <f>IF(AJ41="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ41,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="38">
       <c r="A42" s="51" t="inlineStr">
@@ -6539,6 +7018,17 @@
       <c r="AG42" s="60" t="n"/>
       <c r="AH42" s="60" t="n"/>
       <c r="AI42" s="52" t="n"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42">
+        <f>IF(AJ42="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ42,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN42">
+        <f>IF(AJ42="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ42,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="38">
       <c r="A43" s="51" t="inlineStr">
@@ -6667,6 +7157,17 @@
       <c r="AG43" s="60" t="n"/>
       <c r="AH43" s="60" t="n"/>
       <c r="AI43" s="52" t="n"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43">
+        <f>IF(AJ43="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ43,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN43">
+        <f>IF(AJ43="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ43,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="38">
       <c r="A44" s="51" t="inlineStr">
@@ -6795,6 +7296,17 @@
       <c r="AG44" s="60" t="n"/>
       <c r="AH44" s="60" t="n"/>
       <c r="AI44" s="52" t="n"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44">
+        <f>IF(AJ44="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ44,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN44">
+        <f>IF(AJ44="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ44,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" ht="26.85" customHeight="1" s="38">
       <c r="A45" s="51" t="inlineStr">
@@ -6919,6 +7431,17 @@
       <c r="AG45" s="60" t="n"/>
       <c r="AH45" s="60" t="n"/>
       <c r="AI45" s="52" t="n"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45">
+        <f>IF(AJ45="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ45,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN45">
+        <f>IF(AJ45="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ45,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="38">
       <c r="A46" s="51" t="inlineStr">
@@ -7041,6 +7564,17 @@
       <c r="AG46" s="60" t="n"/>
       <c r="AH46" s="60" t="n"/>
       <c r="AI46" s="52" t="n"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46">
+        <f>IF(AJ46="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ46,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN46">
+        <f>IF(AJ46="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ46,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="38">
       <c r="A47" s="51" t="inlineStr">
@@ -7165,6 +7699,17 @@
       <c r="AG47" s="60" t="n"/>
       <c r="AH47" s="60" t="n"/>
       <c r="AI47" s="52" t="n"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47">
+        <f>IF(AJ47="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ47,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN47">
+        <f>IF(AJ47="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ47,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="38">
       <c r="A48" s="51" t="inlineStr">
@@ -7293,6 +7838,17 @@
       <c r="AG48" s="60" t="n"/>
       <c r="AH48" s="60" t="n"/>
       <c r="AI48" s="52" t="n"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48">
+        <f>IF(AJ48="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ48,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN48">
+        <f>IF(AJ48="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ48,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="38">
       <c r="A49" s="51" t="inlineStr">
@@ -7421,6 +7977,17 @@
       <c r="AG49" s="60" t="n"/>
       <c r="AH49" s="60" t="n"/>
       <c r="AI49" s="52" t="n"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49">
+        <f>IF(AJ49="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ49,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN49">
+        <f>IF(AJ49="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ49,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="38">
       <c r="A50" s="51" t="inlineStr">
@@ -7555,6 +8122,17 @@
       <c r="AG50" s="60" t="n"/>
       <c r="AH50" s="60" t="n"/>
       <c r="AI50" s="52" t="n"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50">
+        <f>IF(AJ50="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ50,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN50">
+        <f>IF(AJ50="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ50,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="38">
       <c r="A51" s="51" t="inlineStr">
@@ -7677,6 +8255,17 @@
       <c r="AG51" s="60" t="n"/>
       <c r="AH51" s="60" t="n"/>
       <c r="AI51" s="52" t="n"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51">
+        <f>IF(AJ51="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ51,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN51">
+        <f>IF(AJ51="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ51,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="38">
       <c r="A52" s="51" t="inlineStr">
@@ -7803,6 +8392,17 @@
       <c r="AG52" s="60" t="n"/>
       <c r="AH52" s="60" t="n"/>
       <c r="AI52" s="52" t="n"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52">
+        <f>IF(AJ52="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ52,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN52">
+        <f>IF(AJ52="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ52,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="38">
       <c r="A53" s="51" t="inlineStr">
@@ -7925,6 +8525,17 @@
       <c r="AG53" s="60" t="n"/>
       <c r="AH53" s="60" t="n"/>
       <c r="AI53" s="52" t="n"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53">
+        <f>IF(AJ53="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ53,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN53">
+        <f>IF(AJ53="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ53,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="26.85" customHeight="1" s="38">
       <c r="A54" s="51" t="inlineStr">
@@ -8053,6 +8664,17 @@
       <c r="AG54" s="60" t="n"/>
       <c r="AH54" s="60" t="n"/>
       <c r="AI54" s="52" t="n"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54">
+        <f>IF(AJ54="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ54,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN54">
+        <f>IF(AJ54="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ54,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="26.85" customHeight="1" s="38">
       <c r="A55" s="51" t="inlineStr">
@@ -8191,6 +8813,17 @@
       <c r="AG55" s="60" t="n"/>
       <c r="AH55" s="60" t="n"/>
       <c r="AI55" s="52" t="n"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55">
+        <f>IF(AJ55="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ55,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN55">
+        <f>IF(AJ55="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ55,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="38">
       <c r="A56" s="51" t="inlineStr">
@@ -8329,6 +8962,17 @@
       <c r="AG56" s="60" t="n"/>
       <c r="AH56" s="60" t="n"/>
       <c r="AI56" s="52" t="n"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56">
+        <f>IF(AJ56="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ56,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN56">
+        <f>IF(AJ56="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ56,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="38">
       <c r="A57" s="51" t="inlineStr">
@@ -8457,6 +9101,17 @@
       <c r="AG57" s="60" t="n"/>
       <c r="AH57" s="60" t="n"/>
       <c r="AI57" s="52" t="n"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57">
+        <f>IF(AJ57="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ57,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN57">
+        <f>IF(AJ57="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ57,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="38">
       <c r="A58" s="51" t="inlineStr">
@@ -8585,6 +9240,17 @@
       <c r="AG58" s="60" t="n"/>
       <c r="AH58" s="60" t="n"/>
       <c r="AI58" s="52" t="n"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58">
+        <f>IF(AJ58="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ58,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN58">
+        <f>IF(AJ58="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ58,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="38">
       <c r="A59" s="51" t="inlineStr">
@@ -8713,6 +9379,17 @@
       <c r="AG59" s="60" t="n"/>
       <c r="AH59" s="60" t="n"/>
       <c r="AI59" s="52" t="n"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59">
+        <f>IF(AJ59="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ59,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN59">
+        <f>IF(AJ59="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ59,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="38">
       <c r="A60" s="51" t="inlineStr">
@@ -8839,6 +9516,17 @@
       <c r="AG60" s="60" t="n"/>
       <c r="AH60" s="60" t="n"/>
       <c r="AI60" s="52" t="n"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60">
+        <f>IF(AJ60="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ60,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN60">
+        <f>IF(AJ60="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ60,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="26.85" customHeight="1" s="38">
       <c r="A61" s="51" t="inlineStr">
@@ -8963,6 +9651,17 @@
       <c r="AG61" s="60" t="n"/>
       <c r="AH61" s="60" t="n"/>
       <c r="AI61" s="52" t="n"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61">
+        <f>IF(AJ61="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ61,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN61">
+        <f>IF(AJ61="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ61,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="38">
       <c r="A62" s="51" t="inlineStr">
@@ -9083,6 +9782,17 @@
       <c r="AG62" s="60" t="n"/>
       <c r="AH62" s="60" t="n"/>
       <c r="AI62" s="52" t="n"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62">
+        <f>IF(AJ62="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ62,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN62">
+        <f>IF(AJ62="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ62,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="38">
       <c r="A63" s="51" t="inlineStr">
@@ -9213,6 +9923,17 @@
       <c r="AG63" s="60" t="n"/>
       <c r="AH63" s="60" t="n"/>
       <c r="AI63" s="52" t="n"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63">
+        <f>IF(AJ63="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ63,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN63">
+        <f>IF(AJ63="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ63,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="38">
       <c r="A64" s="51" t="inlineStr">
@@ -9339,6 +10060,17 @@
       <c r="AG64" s="60" t="n"/>
       <c r="AH64" s="60" t="n"/>
       <c r="AI64" s="52" t="n"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64">
+        <f>IF(AJ64="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ64,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN64">
+        <f>IF(AJ64="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ64,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="38">
       <c r="A65" s="51" t="inlineStr">
@@ -9467,6 +10199,17 @@
       <c r="AG65" s="60" t="n"/>
       <c r="AH65" s="60" t="n"/>
       <c r="AI65" s="52" t="n"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65">
+        <f>IF(AJ65="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ65,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN65">
+        <f>IF(AJ65="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ65,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="38">
       <c r="A66" s="51" t="inlineStr">
@@ -9595,6 +10338,17 @@
       <c r="AG66" s="60" t="n"/>
       <c r="AH66" s="60" t="n"/>
       <c r="AI66" s="52" t="n"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66">
+        <f>IF(AJ66="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ66,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN66">
+        <f>IF(AJ66="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ66,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="67" ht="26.85" customHeight="1" s="38">
       <c r="A67" s="51" t="inlineStr">
@@ -9719,6 +10473,17 @@
       <c r="AG67" s="60" t="n"/>
       <c r="AH67" s="60" t="n"/>
       <c r="AI67" s="52" t="n"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67">
+        <f>IF(AJ67="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ67,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN67">
+        <f>IF(AJ67="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ67,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="38">
       <c r="A68" s="51" t="inlineStr">
@@ -9847,6 +10612,17 @@
       <c r="AG68" s="60" t="n"/>
       <c r="AH68" s="60" t="n"/>
       <c r="AI68" s="52" t="n"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68">
+        <f>IF(AJ68="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ68,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN68">
+        <f>IF(AJ68="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ68,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="26.85" customHeight="1" s="38">
       <c r="A69" s="51" t="inlineStr">
@@ -9989,6 +10765,17 @@
       <c r="AG69" s="60" t="n"/>
       <c r="AH69" s="60" t="n"/>
       <c r="AI69" s="52" t="n"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69">
+        <f>IF(AJ69="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ69,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN69">
+        <f>IF(AJ69="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ69,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="38">
       <c r="A70" s="51" t="inlineStr">
@@ -10117,6 +10904,17 @@
       <c r="AG70" s="60" t="n"/>
       <c r="AH70" s="60" t="n"/>
       <c r="AI70" s="52" t="n"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70">
+        <f>IF(AJ70="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ70,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN70">
+        <f>IF(AJ70="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ70,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="71" ht="26.85" customHeight="1" s="38">
       <c r="A71" s="51" t="inlineStr">
@@ -10241,6 +11039,17 @@
       <c r="AG71" s="60" t="n"/>
       <c r="AH71" s="60" t="n"/>
       <c r="AI71" s="52" t="n"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71">
+        <f>IF(AJ71="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ71,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN71">
+        <f>IF(AJ71="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ71,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="38">
       <c r="A72" s="51" t="inlineStr">
@@ -10369,6 +11178,17 @@
       <c r="AG72" s="60" t="n"/>
       <c r="AH72" s="60" t="n"/>
       <c r="AI72" s="52" t="n"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72">
+        <f>IF(AJ72="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ72,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN72">
+        <f>IF(AJ72="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ72,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="73" ht="26.85" customHeight="1" s="38">
       <c r="A73" s="51" t="inlineStr">
@@ -10497,6 +11317,17 @@
       <c r="AG73" s="60" t="n"/>
       <c r="AH73" s="60" t="n"/>
       <c r="AI73" s="52" t="n"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73">
+        <f>IF(AJ73="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ73,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN73">
+        <f>IF(AJ73="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ73,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="38">
       <c r="A74" s="51" t="inlineStr">
@@ -10623,6 +11454,17 @@
       <c r="AG74" s="60" t="n"/>
       <c r="AH74" s="60" t="n"/>
       <c r="AI74" s="52" t="n"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74">
+        <f>IF(AJ74="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ74,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN74">
+        <f>IF(AJ74="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ74,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="38">
       <c r="A75" s="51" t="inlineStr">
@@ -10751,6 +11593,17 @@
       <c r="AG75" s="60" t="n"/>
       <c r="AH75" s="60" t="n"/>
       <c r="AI75" s="52" t="n"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75">
+        <f>IF(AJ75="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ75,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN75">
+        <f>IF(AJ75="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ75,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="38">
       <c r="A76" s="51" t="inlineStr">
@@ -10879,6 +11732,17 @@
       <c r="AG76" s="60" t="n"/>
       <c r="AH76" s="60" t="n"/>
       <c r="AI76" s="52" t="n"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76">
+        <f>IF(AJ76="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ76,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN76">
+        <f>IF(AJ76="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ76,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="38">
       <c r="A77" s="51" t="inlineStr">
@@ -11003,6 +11867,17 @@
       <c r="AG77" s="60" t="n"/>
       <c r="AH77" s="60" t="n"/>
       <c r="AI77" s="52" t="n"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77">
+        <f>IF(AJ77="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ77,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN77">
+        <f>IF(AJ77="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ77,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="38">
       <c r="A78" s="51" t="inlineStr">
@@ -11141,6 +12016,17 @@
       <c r="AG78" s="60" t="n"/>
       <c r="AH78" s="60" t="n"/>
       <c r="AI78" s="52" t="n"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78">
+        <f>IF(AJ78="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ78,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN78">
+        <f>IF(AJ78="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ78,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="38">
       <c r="A79" s="51" t="inlineStr">
@@ -11263,6 +12149,17 @@
       <c r="AG79" s="60" t="n"/>
       <c r="AH79" s="60" t="n"/>
       <c r="AI79" s="52" t="n"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79">
+        <f>IF(AJ79="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ79,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN79">
+        <f>IF(AJ79="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ79,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="38">
       <c r="A80" s="51" t="inlineStr">
@@ -11389,6 +12286,17 @@
       <c r="AG80" s="60" t="n"/>
       <c r="AH80" s="60" t="n"/>
       <c r="AI80" s="52" t="n"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80">
+        <f>IF(AJ80="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ80,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN80">
+        <f>IF(AJ80="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ80,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="38">
       <c r="A81" s="51" t="inlineStr">
@@ -11517,6 +12425,17 @@
       <c r="AG81" s="60" t="n"/>
       <c r="AH81" s="60" t="n"/>
       <c r="AI81" s="52" t="n"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81">
+        <f>IF(AJ81="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ81,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN81">
+        <f>IF(AJ81="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ81,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="38">
       <c r="A82" s="51" t="inlineStr">
@@ -11645,6 +12564,17 @@
       <c r="AG82" s="60" t="n"/>
       <c r="AH82" s="60" t="n"/>
       <c r="AI82" s="52" t="n"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82">
+        <f>IF(AJ82="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ82,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN82">
+        <f>IF(AJ82="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ82,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="83" ht="26.85" customHeight="1" s="38">
       <c r="A83" s="51" t="inlineStr">
@@ -11769,6 +12699,17 @@
       <c r="AG83" s="60" t="n"/>
       <c r="AH83" s="60" t="n"/>
       <c r="AI83" s="52" t="n"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83">
+        <f>IF(AJ83="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ83,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN83">
+        <f>IF(AJ83="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ83,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="38">
       <c r="A84" s="51" t="inlineStr">
@@ -11901,6 +12842,17 @@
       <c r="AG84" s="60" t="n"/>
       <c r="AH84" s="60" t="n"/>
       <c r="AI84" s="52" t="n"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84">
+        <f>IF(AJ84="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ84,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN84">
+        <f>IF(AJ84="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ84,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="85" ht="26.85" customHeight="1" s="38">
       <c r="A85" s="51" t="inlineStr">
@@ -12039,6 +12991,17 @@
       <c r="AG85" s="60" t="n"/>
       <c r="AH85" s="60" t="n"/>
       <c r="AI85" s="52" t="n"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85">
+        <f>IF(AJ85="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ85,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN85">
+        <f>IF(AJ85="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ85,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="38">
       <c r="A86" s="51" t="inlineStr">
@@ -12165,6 +13128,17 @@
       <c r="AG86" s="60" t="n"/>
       <c r="AH86" s="60" t="n"/>
       <c r="AI86" s="52" t="n"/>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86">
+        <f>IF(AJ86="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ86,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN86">
+        <f>IF(AJ86="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ86,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="38">
       <c r="A87" s="51" t="inlineStr">
@@ -12293,6 +13267,17 @@
       <c r="AG87" s="60" t="n"/>
       <c r="AH87" s="60" t="n"/>
       <c r="AI87" s="52" t="n"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87">
+        <f>IF(AJ87="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ87,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN87">
+        <f>IF(AJ87="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ87,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="38">
       <c r="A88" s="51" t="inlineStr">
@@ -12415,6 +13400,17 @@
       <c r="AG88" s="60" t="n"/>
       <c r="AH88" s="60" t="n"/>
       <c r="AI88" s="52" t="n"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88">
+        <f>IF(AJ88="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ88,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN88">
+        <f>IF(AJ88="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ88,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="38">
       <c r="A89" s="51" t="inlineStr">
@@ -12543,6 +13539,17 @@
       <c r="AG89" s="60" t="n"/>
       <c r="AH89" s="60" t="n"/>
       <c r="AI89" s="52" t="n"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89">
+        <f>IF(AJ89="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ89,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN89">
+        <f>IF(AJ89="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ89,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="90" ht="26.85" customHeight="1" s="38">
       <c r="A90" s="51" t="inlineStr">
@@ -12667,6 +13674,17 @@
       <c r="AG90" s="60" t="n"/>
       <c r="AH90" s="60" t="n"/>
       <c r="AI90" s="52" t="n"/>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90">
+        <f>IF(AJ90="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ90,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN90">
+        <f>IF(AJ90="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ90,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="38">
       <c r="A91" s="51" t="inlineStr">
@@ -12793,6 +13811,17 @@
       <c r="AG91" s="60" t="n"/>
       <c r="AH91" s="60" t="n"/>
       <c r="AI91" s="52" t="n"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91">
+        <f>IF(AJ91="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ91,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN91">
+        <f>IF(AJ91="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ91,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="38">
       <c r="A92" s="51" t="inlineStr">
@@ -12921,6 +13950,17 @@
       <c r="AG92" s="60" t="n"/>
       <c r="AH92" s="60" t="n"/>
       <c r="AI92" s="52" t="n"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92">
+        <f>IF(AJ92="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ92,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN92">
+        <f>IF(AJ92="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ92,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="38">
       <c r="A93" s="51" t="inlineStr">
@@ -13047,6 +14087,17 @@
       <c r="AG93" s="60" t="n"/>
       <c r="AH93" s="60" t="n"/>
       <c r="AI93" s="52" t="n"/>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93">
+        <f>IF(AJ93="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ93,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN93">
+        <f>IF(AJ93="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ93,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="38">
       <c r="A94" s="51" t="inlineStr">
@@ -13173,6 +14224,17 @@
       <c r="AG94" s="60" t="n"/>
       <c r="AH94" s="60" t="n"/>
       <c r="AI94" s="52" t="n"/>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94">
+        <f>IF(AJ94="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ94,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN94">
+        <f>IF(AJ94="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ94,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="38">
       <c r="A95" s="51" t="inlineStr">
@@ -13301,6 +14363,17 @@
       <c r="AG95" s="60" t="n"/>
       <c r="AH95" s="60" t="n"/>
       <c r="AI95" s="52" t="n"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95">
+        <f>IF(AJ95="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ95,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN95">
+        <f>IF(AJ95="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ95,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="38">
       <c r="A96" s="51" t="inlineStr">
@@ -13429,6 +14502,17 @@
       <c r="AG96" s="60" t="n"/>
       <c r="AH96" s="60" t="n"/>
       <c r="AI96" s="52" t="n"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96">
+        <f>IF(AJ96="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ96,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN96">
+        <f>IF(AJ96="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ96,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="97" ht="26.85" customHeight="1" s="38">
       <c r="A97" s="51" t="inlineStr">
@@ -13553,6 +14637,17 @@
       <c r="AG97" s="60" t="n"/>
       <c r="AH97" s="60" t="n"/>
       <c r="AI97" s="52" t="n"/>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97">
+        <f>IF(AJ97="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ97,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN97">
+        <f>IF(AJ97="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ97,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="38">
       <c r="A98" s="51" t="inlineStr">
@@ -13679,6 +14774,17 @@
       <c r="AG98" s="60" t="n"/>
       <c r="AH98" s="60" t="n"/>
       <c r="AI98" s="52" t="n"/>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98">
+        <f>IF(AJ98="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ98,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN98">
+        <f>IF(AJ98="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ98,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="38">
       <c r="A99" s="51" t="inlineStr">
@@ -13803,6 +14909,17 @@
       <c r="AG99" s="60" t="n"/>
       <c r="AH99" s="60" t="n"/>
       <c r="AI99" s="52" t="n"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99">
+        <f>IF(AJ99="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ99,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN99">
+        <f>IF(AJ99="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ99,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="38">
       <c r="A100" s="51" t="inlineStr">
@@ -13933,6 +15050,17 @@
       <c r="AG100" s="60" t="n"/>
       <c r="AH100" s="60" t="n"/>
       <c r="AI100" s="52" t="n"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100">
+        <f>IF(AJ100="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ100,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN100">
+        <f>IF(AJ100="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ100,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="38">
       <c r="A101" s="51" t="inlineStr">
@@ -14061,6 +15189,17 @@
       <c r="AG101" s="60" t="n"/>
       <c r="AH101" s="60" t="n"/>
       <c r="AI101" s="52" t="n"/>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101">
+        <f>IF(AJ101="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ101,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN101">
+        <f>IF(AJ101="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ101,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="102" ht="26.85" customHeight="1" s="38">
       <c r="A102" s="51" t="inlineStr">
@@ -14185,6 +15324,17 @@
       <c r="AG102" s="60" t="n"/>
       <c r="AH102" s="60" t="n"/>
       <c r="AI102" s="52" t="n"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102">
+        <f>IF(AJ102="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ102,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN102">
+        <f>IF(AJ102="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ102,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="38">
       <c r="A103" s="51" t="inlineStr">
@@ -14311,6 +15461,17 @@
       <c r="AG103" s="60" t="n"/>
       <c r="AH103" s="60" t="n"/>
       <c r="AI103" s="52" t="n"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103">
+        <f>IF(AJ103="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ103,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN103">
+        <f>IF(AJ103="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ103,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="38">
       <c r="A104" s="51" t="inlineStr">
@@ -14439,6 +15600,17 @@
       <c r="AG104" s="60" t="n"/>
       <c r="AH104" s="60" t="n"/>
       <c r="AI104" s="52" t="n"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104">
+        <f>IF(AJ104="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ104,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN104">
+        <f>IF(AJ104="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ104,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="38">
       <c r="A105" s="51" t="inlineStr">
@@ -14567,6 +15739,17 @@
       <c r="AG105" s="60" t="n"/>
       <c r="AH105" s="60" t="n"/>
       <c r="AI105" s="52" t="n"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105">
+        <f>IF(AJ105="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ105,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN105">
+        <f>IF(AJ105="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ105,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="106" ht="26.85" customHeight="1" s="38">
       <c r="A106" s="51" t="inlineStr">
@@ -14705,6 +15888,17 @@
       <c r="AG106" s="60" t="n"/>
       <c r="AH106" s="60" t="n"/>
       <c r="AI106" s="52" t="n"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106">
+        <f>IF(AJ106="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ106,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN106">
+        <f>IF(AJ106="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ106,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="38">
       <c r="A108" s="45" t="inlineStr">

--- a/aspirantura_kalkulyator.xlsx
+++ b/aspirantura_kalkulyator.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Розрахунок по ЗВО" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Держзамовлення 2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Джерела" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Держзамовлення 2024 (факт)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Розрахунок по ЗВО'!$A$1:$AI$106</definedName>
@@ -164,7 +165,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -198,6 +199,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -235,7 +241,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -460,6 +466,11 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1388,14 +1399,14 @@
       <c r="AG2" s="60" t="n"/>
       <c r="AH2" s="60" t="n"/>
       <c r="AI2" s="52" t="n"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2">
+      <c r="AJ2" s="37" t="inlineStr"/>
+      <c r="AK2" s="37" t="inlineStr"/>
+      <c r="AL2" s="37" t="inlineStr"/>
+      <c r="AM2" s="37">
         <f>IF(AJ2="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ2,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="37">
         <f>IF(AJ2="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ2,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -1527,14 +1538,14 @@
       <c r="AG3" s="60" t="n"/>
       <c r="AH3" s="60" t="n"/>
       <c r="AI3" s="52" t="n"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3">
+      <c r="AJ3" s="37" t="inlineStr"/>
+      <c r="AK3" s="37" t="inlineStr"/>
+      <c r="AL3" s="37" t="inlineStr"/>
+      <c r="AM3" s="37">
         <f>IF(AJ3="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ3,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="37">
         <f>IF(AJ3="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ3,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -1692,14 +1703,14 @@
       <c r="AG4" s="60" t="n"/>
       <c r="AH4" s="60" t="n"/>
       <c r="AI4" s="52" t="n"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4">
+      <c r="AJ4" s="37" t="inlineStr"/>
+      <c r="AK4" s="37" t="inlineStr"/>
+      <c r="AL4" s="37" t="inlineStr"/>
+      <c r="AM4" s="37">
         <f>IF(AJ4="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ4,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="37">
         <f>IF(AJ4="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ4,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -1827,14 +1838,14 @@
       <c r="AG5" s="60" t="n"/>
       <c r="AH5" s="60" t="n"/>
       <c r="AI5" s="52" t="n"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5">
+      <c r="AJ5" s="37" t="inlineStr"/>
+      <c r="AK5" s="37" t="inlineStr"/>
+      <c r="AL5" s="37" t="inlineStr"/>
+      <c r="AM5" s="37">
         <f>IF(AJ5="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ5,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN5">
+      <c r="AN5" s="37">
         <f>IF(AJ5="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ5,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -1966,14 +1977,14 @@
       <c r="AG6" s="60" t="n"/>
       <c r="AH6" s="60" t="n"/>
       <c r="AI6" s="52" t="n"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6">
+      <c r="AJ6" s="37" t="inlineStr"/>
+      <c r="AK6" s="37" t="inlineStr"/>
+      <c r="AL6" s="37" t="inlineStr"/>
+      <c r="AM6" s="37">
         <f>IF(AJ6="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ6,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN6">
+      <c r="AN6" s="37">
         <f>IF(AJ6="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ6,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -2101,14 +2112,14 @@
       <c r="AG7" s="60" t="n"/>
       <c r="AH7" s="60" t="n"/>
       <c r="AI7" s="52" t="n"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7">
+      <c r="AJ7" s="37" t="inlineStr"/>
+      <c r="AK7" s="37" t="inlineStr"/>
+      <c r="AL7" s="37" t="inlineStr"/>
+      <c r="AM7" s="37">
         <f>IF(AJ7="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ7,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN7">
+      <c r="AN7" s="37">
         <f>IF(AJ7="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ7,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -2236,14 +2247,14 @@
       <c r="AG8" s="60" t="n"/>
       <c r="AH8" s="60" t="n"/>
       <c r="AI8" s="52" t="n"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8">
+      <c r="AJ8" s="37" t="inlineStr"/>
+      <c r="AK8" s="37" t="inlineStr"/>
+      <c r="AL8" s="37" t="inlineStr"/>
+      <c r="AM8" s="37">
         <f>IF(AJ8="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ8,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN8">
+      <c r="AN8" s="37">
         <f>IF(AJ8="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ8,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -2379,14 +2390,14 @@
       <c r="AG9" s="60" t="n"/>
       <c r="AH9" s="60" t="n"/>
       <c r="AI9" s="52" t="n"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9">
+      <c r="AJ9" s="37" t="inlineStr"/>
+      <c r="AK9" s="37" t="inlineStr"/>
+      <c r="AL9" s="37" t="inlineStr"/>
+      <c r="AM9" s="37">
         <f>IF(AJ9="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ9,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN9">
+      <c r="AN9" s="37">
         <f>IF(AJ9="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ9,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -2516,14 +2527,14 @@
       <c r="AG10" s="60" t="n"/>
       <c r="AH10" s="60" t="n"/>
       <c r="AI10" s="52" t="n"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10">
+      <c r="AJ10" s="37" t="inlineStr"/>
+      <c r="AK10" s="37" t="inlineStr"/>
+      <c r="AL10" s="37" t="inlineStr"/>
+      <c r="AM10" s="37">
         <f>IF(AJ10="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ10,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN10">
+      <c r="AN10" s="37">
         <f>IF(AJ10="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ10,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -2669,14 +2680,14 @@
       <c r="AG11" s="60" t="n"/>
       <c r="AH11" s="60" t="n"/>
       <c r="AI11" s="52" t="n"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11">
+      <c r="AJ11" s="37" t="inlineStr"/>
+      <c r="AK11" s="37" t="inlineStr"/>
+      <c r="AL11" s="37" t="inlineStr"/>
+      <c r="AM11" s="37">
         <f>IF(AJ11="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ11,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN11">
+      <c r="AN11" s="37">
         <f>IF(AJ11="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ11,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -2808,14 +2819,14 @@
       <c r="AG12" s="60" t="n"/>
       <c r="AH12" s="60" t="n"/>
       <c r="AI12" s="52" t="n"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12">
+      <c r="AJ12" s="37" t="inlineStr"/>
+      <c r="AK12" s="37" t="inlineStr"/>
+      <c r="AL12" s="37" t="inlineStr"/>
+      <c r="AM12" s="37">
         <f>IF(AJ12="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ12,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN12">
+      <c r="AN12" s="37">
         <f>IF(AJ12="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ12,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -2951,14 +2962,14 @@
       <c r="AG13" s="60" t="n"/>
       <c r="AH13" s="60" t="n"/>
       <c r="AI13" s="52" t="n"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13">
+      <c r="AJ13" s="37" t="inlineStr"/>
+      <c r="AK13" s="37" t="inlineStr"/>
+      <c r="AL13" s="37" t="inlineStr"/>
+      <c r="AM13" s="37">
         <f>IF(AJ13="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ13,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN13">
+      <c r="AN13" s="37">
         <f>IF(AJ13="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ13,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -3090,14 +3101,14 @@
       <c r="AG14" s="60" t="n"/>
       <c r="AH14" s="60" t="n"/>
       <c r="AI14" s="52" t="n"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14">
+      <c r="AJ14" s="37" t="inlineStr"/>
+      <c r="AK14" s="37" t="inlineStr"/>
+      <c r="AL14" s="37" t="inlineStr"/>
+      <c r="AM14" s="37">
         <f>IF(AJ14="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ14,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN14">
+      <c r="AN14" s="37">
         <f>IF(AJ14="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ14,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -3233,14 +3244,14 @@
       <c r="AG15" s="60" t="n"/>
       <c r="AH15" s="60" t="n"/>
       <c r="AI15" s="52" t="n"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15">
+      <c r="AJ15" s="37" t="inlineStr"/>
+      <c r="AK15" s="37" t="inlineStr"/>
+      <c r="AL15" s="37" t="inlineStr"/>
+      <c r="AM15" s="37">
         <f>IF(AJ15="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ15,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN15">
+      <c r="AN15" s="37">
         <f>IF(AJ15="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ15,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -3370,14 +3381,14 @@
       <c r="AG16" s="60" t="n"/>
       <c r="AH16" s="60" t="n"/>
       <c r="AI16" s="52" t="n"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16">
+      <c r="AJ16" s="37" t="inlineStr"/>
+      <c r="AK16" s="37" t="inlineStr"/>
+      <c r="AL16" s="37" t="inlineStr"/>
+      <c r="AM16" s="37">
         <f>IF(AJ16="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ16,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN16">
+      <c r="AN16" s="37">
         <f>IF(AJ16="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ16,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -3513,14 +3524,14 @@
       <c r="AG17" s="60" t="n"/>
       <c r="AH17" s="60" t="n"/>
       <c r="AI17" s="52" t="n"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17">
+      <c r="AJ17" s="37" t="inlineStr"/>
+      <c r="AK17" s="37" t="inlineStr"/>
+      <c r="AL17" s="37" t="inlineStr"/>
+      <c r="AM17" s="37">
         <f>IF(AJ17="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ17,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN17">
+      <c r="AN17" s="37">
         <f>IF(AJ17="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ17,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -3658,14 +3669,14 @@
       <c r="AG18" s="60" t="n"/>
       <c r="AH18" s="60" t="n"/>
       <c r="AI18" s="52" t="n"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18">
+      <c r="AJ18" s="37" t="inlineStr"/>
+      <c r="AK18" s="37" t="inlineStr"/>
+      <c r="AL18" s="37" t="inlineStr"/>
+      <c r="AM18" s="37">
         <f>IF(AJ18="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ18,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN18">
+      <c r="AN18" s="37">
         <f>IF(AJ18="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ18,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -3793,14 +3804,14 @@
       <c r="AG19" s="60" t="n"/>
       <c r="AH19" s="60" t="n"/>
       <c r="AI19" s="52" t="n"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19">
+      <c r="AJ19" s="37" t="inlineStr"/>
+      <c r="AK19" s="37" t="inlineStr"/>
+      <c r="AL19" s="37" t="inlineStr"/>
+      <c r="AM19" s="37">
         <f>IF(AJ19="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ19,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN19">
+      <c r="AN19" s="37">
         <f>IF(AJ19="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ19,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -3928,14 +3939,14 @@
       <c r="AG20" s="60" t="n"/>
       <c r="AH20" s="60" t="n"/>
       <c r="AI20" s="52" t="n"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20">
+      <c r="AJ20" s="37" t="inlineStr"/>
+      <c r="AK20" s="37" t="inlineStr"/>
+      <c r="AL20" s="37" t="inlineStr"/>
+      <c r="AM20" s="37">
         <f>IF(AJ20="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ20,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN20">
+      <c r="AN20" s="37">
         <f>IF(AJ20="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ20,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -4065,14 +4076,14 @@
       <c r="AG21" s="60" t="n"/>
       <c r="AH21" s="60" t="n"/>
       <c r="AI21" s="52" t="n"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21">
+      <c r="AJ21" s="37" t="inlineStr"/>
+      <c r="AK21" s="37" t="inlineStr"/>
+      <c r="AL21" s="37" t="inlineStr"/>
+      <c r="AM21" s="37">
         <f>IF(AJ21="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ21,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN21">
+      <c r="AN21" s="37">
         <f>IF(AJ21="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ21,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -4218,14 +4229,14 @@
       <c r="AG22" s="60" t="n"/>
       <c r="AH22" s="60" t="n"/>
       <c r="AI22" s="52" t="n"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22">
+      <c r="AJ22" s="37" t="inlineStr"/>
+      <c r="AK22" s="37" t="inlineStr"/>
+      <c r="AL22" s="37" t="inlineStr"/>
+      <c r="AM22" s="37">
         <f>IF(AJ22="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ22,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN22">
+      <c r="AN22" s="37">
         <f>IF(AJ22="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ22,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -4357,14 +4368,14 @@
       <c r="AG23" s="60" t="n"/>
       <c r="AH23" s="60" t="n"/>
       <c r="AI23" s="52" t="n"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23">
+      <c r="AJ23" s="37" t="inlineStr"/>
+      <c r="AK23" s="37" t="inlineStr"/>
+      <c r="AL23" s="37" t="inlineStr"/>
+      <c r="AM23" s="37">
         <f>IF(AJ23="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ23,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN23">
+      <c r="AN23" s="37">
         <f>IF(AJ23="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ23,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -4490,14 +4501,14 @@
       <c r="AG24" s="60" t="n"/>
       <c r="AH24" s="60" t="n"/>
       <c r="AI24" s="52" t="n"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24">
+      <c r="AJ24" s="37" t="inlineStr"/>
+      <c r="AK24" s="37" t="inlineStr"/>
+      <c r="AL24" s="37" t="inlineStr"/>
+      <c r="AM24" s="37">
         <f>IF(AJ24="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ24,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN24">
+      <c r="AN24" s="37">
         <f>IF(AJ24="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ24,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -4633,14 +4644,14 @@
       <c r="AG25" s="60" t="n"/>
       <c r="AH25" s="60" t="n"/>
       <c r="AI25" s="52" t="n"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25">
+      <c r="AJ25" s="37" t="inlineStr"/>
+      <c r="AK25" s="37" t="inlineStr"/>
+      <c r="AL25" s="37" t="inlineStr"/>
+      <c r="AM25" s="37">
         <f>IF(AJ25="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ25,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN25">
+      <c r="AN25" s="37">
         <f>IF(AJ25="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ25,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -4772,14 +4783,14 @@
       <c r="AG26" s="60" t="n"/>
       <c r="AH26" s="60" t="n"/>
       <c r="AI26" s="52" t="n"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26">
+      <c r="AJ26" s="37" t="inlineStr"/>
+      <c r="AK26" s="37" t="inlineStr"/>
+      <c r="AL26" s="37" t="inlineStr"/>
+      <c r="AM26" s="37">
         <f>IF(AJ26="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ26,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN26">
+      <c r="AN26" s="37">
         <f>IF(AJ26="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ26,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -4909,14 +4920,14 @@
       <c r="AG27" s="60" t="n"/>
       <c r="AH27" s="60" t="n"/>
       <c r="AI27" s="52" t="n"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27">
+      <c r="AJ27" s="37" t="inlineStr"/>
+      <c r="AK27" s="37" t="inlineStr"/>
+      <c r="AL27" s="37" t="inlineStr"/>
+      <c r="AM27" s="37">
         <f>IF(AJ27="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ27,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN27">
+      <c r="AN27" s="37">
         <f>IF(AJ27="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ27,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -5044,14 +5055,14 @@
       <c r="AG28" s="60" t="n"/>
       <c r="AH28" s="60" t="n"/>
       <c r="AI28" s="52" t="n"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28">
+      <c r="AJ28" s="37" t="inlineStr"/>
+      <c r="AK28" s="37" t="inlineStr"/>
+      <c r="AL28" s="37" t="inlineStr"/>
+      <c r="AM28" s="37">
         <f>IF(AJ28="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ28,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN28">
+      <c r="AN28" s="37">
         <f>IF(AJ28="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ28,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -5197,14 +5208,14 @@
       <c r="AG29" s="60" t="n"/>
       <c r="AH29" s="60" t="n"/>
       <c r="AI29" s="52" t="n"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29">
+      <c r="AJ29" s="37" t="inlineStr"/>
+      <c r="AK29" s="37" t="inlineStr"/>
+      <c r="AL29" s="37" t="inlineStr"/>
+      <c r="AM29" s="37">
         <f>IF(AJ29="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ29,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN29">
+      <c r="AN29" s="37">
         <f>IF(AJ29="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ29,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -5338,14 +5349,14 @@
       <c r="AG30" s="60" t="n"/>
       <c r="AH30" s="60" t="n"/>
       <c r="AI30" s="52" t="n"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30">
+      <c r="AJ30" s="37" t="inlineStr"/>
+      <c r="AK30" s="37" t="inlineStr"/>
+      <c r="AL30" s="37" t="inlineStr"/>
+      <c r="AM30" s="37">
         <f>IF(AJ30="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ30,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN30">
+      <c r="AN30" s="37">
         <f>IF(AJ30="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ30,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -5477,14 +5488,14 @@
       <c r="AG31" s="60" t="n"/>
       <c r="AH31" s="60" t="n"/>
       <c r="AI31" s="52" t="n"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31">
+      <c r="AJ31" s="37" t="inlineStr"/>
+      <c r="AK31" s="37" t="inlineStr"/>
+      <c r="AL31" s="37" t="inlineStr"/>
+      <c r="AM31" s="37">
         <f>IF(AJ31="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ31,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN31">
+      <c r="AN31" s="37">
         <f>IF(AJ31="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ31,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -5610,14 +5621,14 @@
       <c r="AG32" s="60" t="n"/>
       <c r="AH32" s="60" t="n"/>
       <c r="AI32" s="52" t="n"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32">
+      <c r="AJ32" s="37" t="inlineStr"/>
+      <c r="AK32" s="37" t="inlineStr"/>
+      <c r="AL32" s="37" t="inlineStr"/>
+      <c r="AM32" s="37">
         <f>IF(AJ32="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ32,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN32">
+      <c r="AN32" s="37">
         <f>IF(AJ32="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ32,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -5749,14 +5760,14 @@
       <c r="AG33" s="60" t="n"/>
       <c r="AH33" s="60" t="n"/>
       <c r="AI33" s="52" t="n"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33">
+      <c r="AJ33" s="37" t="inlineStr"/>
+      <c r="AK33" s="37" t="inlineStr"/>
+      <c r="AL33" s="37" t="inlineStr"/>
+      <c r="AM33" s="37">
         <f>IF(AJ33="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ33,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN33">
+      <c r="AN33" s="37">
         <f>IF(AJ33="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ33,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -5902,14 +5913,14 @@
       <c r="AG34" s="60" t="n"/>
       <c r="AH34" s="60" t="n"/>
       <c r="AI34" s="52" t="n"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34">
+      <c r="AJ34" s="37" t="inlineStr"/>
+      <c r="AK34" s="37" t="inlineStr"/>
+      <c r="AL34" s="37" t="inlineStr"/>
+      <c r="AM34" s="37">
         <f>IF(AJ34="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ34,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN34">
+      <c r="AN34" s="37">
         <f>IF(AJ34="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ34,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -6037,14 +6048,14 @@
       <c r="AG35" s="60" t="n"/>
       <c r="AH35" s="60" t="n"/>
       <c r="AI35" s="52" t="n"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35">
+      <c r="AJ35" s="37" t="inlineStr"/>
+      <c r="AK35" s="37" t="inlineStr"/>
+      <c r="AL35" s="37" t="inlineStr"/>
+      <c r="AM35" s="37">
         <f>IF(AJ35="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ35,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN35">
+      <c r="AN35" s="37">
         <f>IF(AJ35="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ35,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -6178,14 +6189,14 @@
       <c r="AG36" s="60" t="n"/>
       <c r="AH36" s="60" t="n"/>
       <c r="AI36" s="52" t="n"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36">
+      <c r="AJ36" s="37" t="inlineStr"/>
+      <c r="AK36" s="37" t="inlineStr"/>
+      <c r="AL36" s="37" t="inlineStr"/>
+      <c r="AM36" s="37">
         <f>IF(AJ36="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ36,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN36">
+      <c r="AN36" s="37">
         <f>IF(AJ36="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ36,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -6313,14 +6324,14 @@
       <c r="AG37" s="60" t="n"/>
       <c r="AH37" s="60" t="n"/>
       <c r="AI37" s="52" t="n"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37">
+      <c r="AJ37" s="37" t="inlineStr"/>
+      <c r="AK37" s="37" t="inlineStr"/>
+      <c r="AL37" s="37" t="inlineStr"/>
+      <c r="AM37" s="37">
         <f>IF(AJ37="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ37,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN37">
+      <c r="AN37" s="37">
         <f>IF(AJ37="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ37,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -6448,14 +6459,14 @@
       <c r="AG38" s="60" t="n"/>
       <c r="AH38" s="60" t="n"/>
       <c r="AI38" s="52" t="n"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38">
+      <c r="AJ38" s="37" t="inlineStr"/>
+      <c r="AK38" s="37" t="inlineStr"/>
+      <c r="AL38" s="37" t="inlineStr"/>
+      <c r="AM38" s="37">
         <f>IF(AJ38="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ38,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN38">
+      <c r="AN38" s="37">
         <f>IF(AJ38="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ38,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -6589,14 +6600,14 @@
       <c r="AG39" s="60" t="n"/>
       <c r="AH39" s="60" t="n"/>
       <c r="AI39" s="52" t="n"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39">
+      <c r="AJ39" s="37" t="inlineStr"/>
+      <c r="AK39" s="37" t="inlineStr"/>
+      <c r="AL39" s="37" t="inlineStr"/>
+      <c r="AM39" s="37">
         <f>IF(AJ39="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ39,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN39">
+      <c r="AN39" s="37">
         <f>IF(AJ39="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ39,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -6742,14 +6753,14 @@
       <c r="AG40" s="60" t="n"/>
       <c r="AH40" s="60" t="n"/>
       <c r="AI40" s="52" t="n"/>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40">
+      <c r="AJ40" s="37" t="inlineStr"/>
+      <c r="AK40" s="37" t="inlineStr"/>
+      <c r="AL40" s="37" t="inlineStr"/>
+      <c r="AM40" s="37">
         <f>IF(AJ40="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ40,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN40">
+      <c r="AN40" s="37">
         <f>IF(AJ40="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ40,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -6879,14 +6890,14 @@
       <c r="AG41" s="60" t="n"/>
       <c r="AH41" s="60" t="n"/>
       <c r="AI41" s="52" t="n"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41">
+      <c r="AJ41" s="37" t="inlineStr"/>
+      <c r="AK41" s="37" t="inlineStr"/>
+      <c r="AL41" s="37" t="inlineStr"/>
+      <c r="AM41" s="37">
         <f>IF(AJ41="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ41,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN41">
+      <c r="AN41" s="37">
         <f>IF(AJ41="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ41,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -7018,14 +7029,14 @@
       <c r="AG42" s="60" t="n"/>
       <c r="AH42" s="60" t="n"/>
       <c r="AI42" s="52" t="n"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42">
+      <c r="AJ42" s="37" t="inlineStr"/>
+      <c r="AK42" s="37" t="inlineStr"/>
+      <c r="AL42" s="37" t="inlineStr"/>
+      <c r="AM42" s="37">
         <f>IF(AJ42="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ42,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN42">
+      <c r="AN42" s="37">
         <f>IF(AJ42="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ42,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -7157,14 +7168,14 @@
       <c r="AG43" s="60" t="n"/>
       <c r="AH43" s="60" t="n"/>
       <c r="AI43" s="52" t="n"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43">
+      <c r="AJ43" s="37" t="inlineStr"/>
+      <c r="AK43" s="37" t="inlineStr"/>
+      <c r="AL43" s="37" t="inlineStr"/>
+      <c r="AM43" s="37">
         <f>IF(AJ43="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ43,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN43">
+      <c r="AN43" s="37">
         <f>IF(AJ43="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ43,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -7296,14 +7307,14 @@
       <c r="AG44" s="60" t="n"/>
       <c r="AH44" s="60" t="n"/>
       <c r="AI44" s="52" t="n"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44">
+      <c r="AJ44" s="37" t="inlineStr"/>
+      <c r="AK44" s="37" t="inlineStr"/>
+      <c r="AL44" s="37" t="inlineStr"/>
+      <c r="AM44" s="37">
         <f>IF(AJ44="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ44,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN44">
+      <c r="AN44" s="37">
         <f>IF(AJ44="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ44,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -7431,14 +7442,14 @@
       <c r="AG45" s="60" t="n"/>
       <c r="AH45" s="60" t="n"/>
       <c r="AI45" s="52" t="n"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45">
+      <c r="AJ45" s="37" t="inlineStr"/>
+      <c r="AK45" s="37" t="inlineStr"/>
+      <c r="AL45" s="37" t="inlineStr"/>
+      <c r="AM45" s="37">
         <f>IF(AJ45="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ45,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN45">
+      <c r="AN45" s="37">
         <f>IF(AJ45="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ45,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -7564,14 +7575,14 @@
       <c r="AG46" s="60" t="n"/>
       <c r="AH46" s="60" t="n"/>
       <c r="AI46" s="52" t="n"/>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46">
+      <c r="AJ46" s="37" t="inlineStr"/>
+      <c r="AK46" s="37" t="inlineStr"/>
+      <c r="AL46" s="37" t="inlineStr"/>
+      <c r="AM46" s="37">
         <f>IF(AJ46="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ46,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN46">
+      <c r="AN46" s="37">
         <f>IF(AJ46="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ46,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -7699,14 +7710,14 @@
       <c r="AG47" s="60" t="n"/>
       <c r="AH47" s="60" t="n"/>
       <c r="AI47" s="52" t="n"/>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47">
+      <c r="AJ47" s="37" t="inlineStr"/>
+      <c r="AK47" s="37" t="inlineStr"/>
+      <c r="AL47" s="37" t="inlineStr"/>
+      <c r="AM47" s="37">
         <f>IF(AJ47="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ47,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN47">
+      <c r="AN47" s="37">
         <f>IF(AJ47="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ47,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -7838,14 +7849,14 @@
       <c r="AG48" s="60" t="n"/>
       <c r="AH48" s="60" t="n"/>
       <c r="AI48" s="52" t="n"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48">
+      <c r="AJ48" s="37" t="inlineStr"/>
+      <c r="AK48" s="37" t="inlineStr"/>
+      <c r="AL48" s="37" t="inlineStr"/>
+      <c r="AM48" s="37">
         <f>IF(AJ48="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ48,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN48">
+      <c r="AN48" s="37">
         <f>IF(AJ48="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ48,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -7977,14 +7988,14 @@
       <c r="AG49" s="60" t="n"/>
       <c r="AH49" s="60" t="n"/>
       <c r="AI49" s="52" t="n"/>
-      <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49">
+      <c r="AJ49" s="37" t="inlineStr"/>
+      <c r="AK49" s="37" t="inlineStr"/>
+      <c r="AL49" s="37" t="inlineStr"/>
+      <c r="AM49" s="37">
         <f>IF(AJ49="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ49,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN49">
+      <c r="AN49" s="37">
         <f>IF(AJ49="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ49,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -8122,14 +8133,14 @@
       <c r="AG50" s="60" t="n"/>
       <c r="AH50" s="60" t="n"/>
       <c r="AI50" s="52" t="n"/>
-      <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50">
+      <c r="AJ50" s="37" t="inlineStr"/>
+      <c r="AK50" s="37" t="inlineStr"/>
+      <c r="AL50" s="37" t="inlineStr"/>
+      <c r="AM50" s="37">
         <f>IF(AJ50="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ50,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN50">
+      <c r="AN50" s="37">
         <f>IF(AJ50="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ50,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -8255,14 +8266,14 @@
       <c r="AG51" s="60" t="n"/>
       <c r="AH51" s="60" t="n"/>
       <c r="AI51" s="52" t="n"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51">
+      <c r="AJ51" s="37" t="inlineStr"/>
+      <c r="AK51" s="37" t="inlineStr"/>
+      <c r="AL51" s="37" t="inlineStr"/>
+      <c r="AM51" s="37">
         <f>IF(AJ51="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ51,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN51">
+      <c r="AN51" s="37">
         <f>IF(AJ51="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ51,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -8392,14 +8403,14 @@
       <c r="AG52" s="60" t="n"/>
       <c r="AH52" s="60" t="n"/>
       <c r="AI52" s="52" t="n"/>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52">
+      <c r="AJ52" s="37" t="inlineStr"/>
+      <c r="AK52" s="37" t="inlineStr"/>
+      <c r="AL52" s="37" t="inlineStr"/>
+      <c r="AM52" s="37">
         <f>IF(AJ52="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ52,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN52">
+      <c r="AN52" s="37">
         <f>IF(AJ52="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ52,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -8525,14 +8536,14 @@
       <c r="AG53" s="60" t="n"/>
       <c r="AH53" s="60" t="n"/>
       <c r="AI53" s="52" t="n"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53">
+      <c r="AJ53" s="37" t="inlineStr"/>
+      <c r="AK53" s="37" t="inlineStr"/>
+      <c r="AL53" s="37" t="inlineStr"/>
+      <c r="AM53" s="37">
         <f>IF(AJ53="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ53,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN53">
+      <c r="AN53" s="37">
         <f>IF(AJ53="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ53,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -8664,14 +8675,14 @@
       <c r="AG54" s="60" t="n"/>
       <c r="AH54" s="60" t="n"/>
       <c r="AI54" s="52" t="n"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54">
+      <c r="AJ54" s="37" t="inlineStr"/>
+      <c r="AK54" s="37" t="inlineStr"/>
+      <c r="AL54" s="37" t="inlineStr"/>
+      <c r="AM54" s="37">
         <f>IF(AJ54="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ54,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN54">
+      <c r="AN54" s="37">
         <f>IF(AJ54="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ54,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -8813,14 +8824,14 @@
       <c r="AG55" s="60" t="n"/>
       <c r="AH55" s="60" t="n"/>
       <c r="AI55" s="52" t="n"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55">
+      <c r="AJ55" s="37" t="inlineStr"/>
+      <c r="AK55" s="37" t="inlineStr"/>
+      <c r="AL55" s="37" t="inlineStr"/>
+      <c r="AM55" s="37">
         <f>IF(AJ55="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ55,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN55">
+      <c r="AN55" s="37">
         <f>IF(AJ55="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ55,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -8962,14 +8973,14 @@
       <c r="AG56" s="60" t="n"/>
       <c r="AH56" s="60" t="n"/>
       <c r="AI56" s="52" t="n"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56">
+      <c r="AJ56" s="37" t="inlineStr"/>
+      <c r="AK56" s="37" t="inlineStr"/>
+      <c r="AL56" s="37" t="inlineStr"/>
+      <c r="AM56" s="37">
         <f>IF(AJ56="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ56,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN56">
+      <c r="AN56" s="37">
         <f>IF(AJ56="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ56,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -9101,14 +9112,14 @@
       <c r="AG57" s="60" t="n"/>
       <c r="AH57" s="60" t="n"/>
       <c r="AI57" s="52" t="n"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57">
+      <c r="AJ57" s="37" t="inlineStr"/>
+      <c r="AK57" s="37" t="inlineStr"/>
+      <c r="AL57" s="37" t="inlineStr"/>
+      <c r="AM57" s="37">
         <f>IF(AJ57="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ57,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN57">
+      <c r="AN57" s="37">
         <f>IF(AJ57="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ57,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -9240,14 +9251,14 @@
       <c r="AG58" s="60" t="n"/>
       <c r="AH58" s="60" t="n"/>
       <c r="AI58" s="52" t="n"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58">
+      <c r="AJ58" s="37" t="inlineStr"/>
+      <c r="AK58" s="37" t="inlineStr"/>
+      <c r="AL58" s="37" t="inlineStr"/>
+      <c r="AM58" s="37">
         <f>IF(AJ58="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ58,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN58">
+      <c r="AN58" s="37">
         <f>IF(AJ58="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ58,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -9379,14 +9390,14 @@
       <c r="AG59" s="60" t="n"/>
       <c r="AH59" s="60" t="n"/>
       <c r="AI59" s="52" t="n"/>
-      <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59">
+      <c r="AJ59" s="37" t="inlineStr"/>
+      <c r="AK59" s="37" t="inlineStr"/>
+      <c r="AL59" s="37" t="inlineStr"/>
+      <c r="AM59" s="37">
         <f>IF(AJ59="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ59,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN59">
+      <c r="AN59" s="37">
         <f>IF(AJ59="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ59,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -9516,14 +9527,14 @@
       <c r="AG60" s="60" t="n"/>
       <c r="AH60" s="60" t="n"/>
       <c r="AI60" s="52" t="n"/>
-      <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60">
+      <c r="AJ60" s="37" t="inlineStr"/>
+      <c r="AK60" s="37" t="inlineStr"/>
+      <c r="AL60" s="37" t="inlineStr"/>
+      <c r="AM60" s="37">
         <f>IF(AJ60="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ60,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN60">
+      <c r="AN60" s="37">
         <f>IF(AJ60="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ60,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -9651,14 +9662,14 @@
       <c r="AG61" s="60" t="n"/>
       <c r="AH61" s="60" t="n"/>
       <c r="AI61" s="52" t="n"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61">
+      <c r="AJ61" s="37" t="inlineStr"/>
+      <c r="AK61" s="37" t="inlineStr"/>
+      <c r="AL61" s="37" t="inlineStr"/>
+      <c r="AM61" s="37">
         <f>IF(AJ61="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ61,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN61">
+      <c r="AN61" s="37">
         <f>IF(AJ61="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ61,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -9782,14 +9793,14 @@
       <c r="AG62" s="60" t="n"/>
       <c r="AH62" s="60" t="n"/>
       <c r="AI62" s="52" t="n"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62">
+      <c r="AJ62" s="37" t="inlineStr"/>
+      <c r="AK62" s="37" t="inlineStr"/>
+      <c r="AL62" s="37" t="inlineStr"/>
+      <c r="AM62" s="37">
         <f>IF(AJ62="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ62,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN62">
+      <c r="AN62" s="37">
         <f>IF(AJ62="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ62,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -9923,14 +9934,14 @@
       <c r="AG63" s="60" t="n"/>
       <c r="AH63" s="60" t="n"/>
       <c r="AI63" s="52" t="n"/>
-      <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63">
+      <c r="AJ63" s="37" t="inlineStr"/>
+      <c r="AK63" s="37" t="inlineStr"/>
+      <c r="AL63" s="37" t="inlineStr"/>
+      <c r="AM63" s="37">
         <f>IF(AJ63="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ63,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN63">
+      <c r="AN63" s="37">
         <f>IF(AJ63="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ63,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -10060,14 +10071,14 @@
       <c r="AG64" s="60" t="n"/>
       <c r="AH64" s="60" t="n"/>
       <c r="AI64" s="52" t="n"/>
-      <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64">
+      <c r="AJ64" s="37" t="inlineStr"/>
+      <c r="AK64" s="37" t="inlineStr"/>
+      <c r="AL64" s="37" t="inlineStr"/>
+      <c r="AM64" s="37">
         <f>IF(AJ64="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ64,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN64">
+      <c r="AN64" s="37">
         <f>IF(AJ64="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ64,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -10199,14 +10210,14 @@
       <c r="AG65" s="60" t="n"/>
       <c r="AH65" s="60" t="n"/>
       <c r="AI65" s="52" t="n"/>
-      <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65">
+      <c r="AJ65" s="37" t="inlineStr"/>
+      <c r="AK65" s="37" t="inlineStr"/>
+      <c r="AL65" s="37" t="inlineStr"/>
+      <c r="AM65" s="37">
         <f>IF(AJ65="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ65,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN65">
+      <c r="AN65" s="37">
         <f>IF(AJ65="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ65,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -10338,14 +10349,14 @@
       <c r="AG66" s="60" t="n"/>
       <c r="AH66" s="60" t="n"/>
       <c r="AI66" s="52" t="n"/>
-      <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66">
+      <c r="AJ66" s="37" t="inlineStr"/>
+      <c r="AK66" s="37" t="inlineStr"/>
+      <c r="AL66" s="37" t="inlineStr"/>
+      <c r="AM66" s="37">
         <f>IF(AJ66="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ66,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN66">
+      <c r="AN66" s="37">
         <f>IF(AJ66="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ66,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -10473,14 +10484,14 @@
       <c r="AG67" s="60" t="n"/>
       <c r="AH67" s="60" t="n"/>
       <c r="AI67" s="52" t="n"/>
-      <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="inlineStr"/>
-      <c r="AL67" t="inlineStr"/>
-      <c r="AM67">
+      <c r="AJ67" s="37" t="inlineStr"/>
+      <c r="AK67" s="37" t="inlineStr"/>
+      <c r="AL67" s="37" t="inlineStr"/>
+      <c r="AM67" s="37">
         <f>IF(AJ67="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ67,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN67">
+      <c r="AN67" s="37">
         <f>IF(AJ67="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ67,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -10612,14 +10623,14 @@
       <c r="AG68" s="60" t="n"/>
       <c r="AH68" s="60" t="n"/>
       <c r="AI68" s="52" t="n"/>
-      <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="inlineStr"/>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68">
+      <c r="AJ68" s="37" t="inlineStr"/>
+      <c r="AK68" s="37" t="inlineStr"/>
+      <c r="AL68" s="37" t="inlineStr"/>
+      <c r="AM68" s="37">
         <f>IF(AJ68="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ68,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN68">
+      <c r="AN68" s="37">
         <f>IF(AJ68="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ68,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -10765,14 +10776,14 @@
       <c r="AG69" s="60" t="n"/>
       <c r="AH69" s="60" t="n"/>
       <c r="AI69" s="52" t="n"/>
-      <c r="AJ69" t="inlineStr"/>
-      <c r="AK69" t="inlineStr"/>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69">
+      <c r="AJ69" s="37" t="inlineStr"/>
+      <c r="AK69" s="37" t="inlineStr"/>
+      <c r="AL69" s="37" t="inlineStr"/>
+      <c r="AM69" s="37">
         <f>IF(AJ69="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ69,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN69">
+      <c r="AN69" s="37">
         <f>IF(AJ69="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ69,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -10904,14 +10915,14 @@
       <c r="AG70" s="60" t="n"/>
       <c r="AH70" s="60" t="n"/>
       <c r="AI70" s="52" t="n"/>
-      <c r="AJ70" t="inlineStr"/>
-      <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70">
+      <c r="AJ70" s="37" t="inlineStr"/>
+      <c r="AK70" s="37" t="inlineStr"/>
+      <c r="AL70" s="37" t="inlineStr"/>
+      <c r="AM70" s="37">
         <f>IF(AJ70="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ70,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN70">
+      <c r="AN70" s="37">
         <f>IF(AJ70="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ70,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -11039,14 +11050,14 @@
       <c r="AG71" s="60" t="n"/>
       <c r="AH71" s="60" t="n"/>
       <c r="AI71" s="52" t="n"/>
-      <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr"/>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71">
+      <c r="AJ71" s="37" t="inlineStr"/>
+      <c r="AK71" s="37" t="inlineStr"/>
+      <c r="AL71" s="37" t="inlineStr"/>
+      <c r="AM71" s="37">
         <f>IF(AJ71="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ71,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN71">
+      <c r="AN71" s="37">
         <f>IF(AJ71="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ71,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -11178,14 +11189,14 @@
       <c r="AG72" s="60" t="n"/>
       <c r="AH72" s="60" t="n"/>
       <c r="AI72" s="52" t="n"/>
-      <c r="AJ72" t="inlineStr"/>
-      <c r="AK72" t="inlineStr"/>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72">
+      <c r="AJ72" s="37" t="inlineStr"/>
+      <c r="AK72" s="37" t="inlineStr"/>
+      <c r="AL72" s="37" t="inlineStr"/>
+      <c r="AM72" s="37">
         <f>IF(AJ72="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ72,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN72">
+      <c r="AN72" s="37">
         <f>IF(AJ72="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ72,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -11317,14 +11328,14 @@
       <c r="AG73" s="60" t="n"/>
       <c r="AH73" s="60" t="n"/>
       <c r="AI73" s="52" t="n"/>
-      <c r="AJ73" t="inlineStr"/>
-      <c r="AK73" t="inlineStr"/>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73">
+      <c r="AJ73" s="37" t="inlineStr"/>
+      <c r="AK73" s="37" t="inlineStr"/>
+      <c r="AL73" s="37" t="inlineStr"/>
+      <c r="AM73" s="37">
         <f>IF(AJ73="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ73,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN73">
+      <c r="AN73" s="37">
         <f>IF(AJ73="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ73,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -11454,14 +11465,14 @@
       <c r="AG74" s="60" t="n"/>
       <c r="AH74" s="60" t="n"/>
       <c r="AI74" s="52" t="n"/>
-      <c r="AJ74" t="inlineStr"/>
-      <c r="AK74" t="inlineStr"/>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74">
+      <c r="AJ74" s="37" t="inlineStr"/>
+      <c r="AK74" s="37" t="inlineStr"/>
+      <c r="AL74" s="37" t="inlineStr"/>
+      <c r="AM74" s="37">
         <f>IF(AJ74="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ74,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN74">
+      <c r="AN74" s="37">
         <f>IF(AJ74="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ74,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -11593,14 +11604,14 @@
       <c r="AG75" s="60" t="n"/>
       <c r="AH75" s="60" t="n"/>
       <c r="AI75" s="52" t="n"/>
-      <c r="AJ75" t="inlineStr"/>
-      <c r="AK75" t="inlineStr"/>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75">
+      <c r="AJ75" s="37" t="inlineStr"/>
+      <c r="AK75" s="37" t="inlineStr"/>
+      <c r="AL75" s="37" t="inlineStr"/>
+      <c r="AM75" s="37">
         <f>IF(AJ75="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ75,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN75">
+      <c r="AN75" s="37">
         <f>IF(AJ75="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ75,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -11732,14 +11743,14 @@
       <c r="AG76" s="60" t="n"/>
       <c r="AH76" s="60" t="n"/>
       <c r="AI76" s="52" t="n"/>
-      <c r="AJ76" t="inlineStr"/>
-      <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76">
+      <c r="AJ76" s="37" t="inlineStr"/>
+      <c r="AK76" s="37" t="inlineStr"/>
+      <c r="AL76" s="37" t="inlineStr"/>
+      <c r="AM76" s="37">
         <f>IF(AJ76="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ76,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN76">
+      <c r="AN76" s="37">
         <f>IF(AJ76="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ76,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -11867,14 +11878,14 @@
       <c r="AG77" s="60" t="n"/>
       <c r="AH77" s="60" t="n"/>
       <c r="AI77" s="52" t="n"/>
-      <c r="AJ77" t="inlineStr"/>
-      <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77">
+      <c r="AJ77" s="37" t="inlineStr"/>
+      <c r="AK77" s="37" t="inlineStr"/>
+      <c r="AL77" s="37" t="inlineStr"/>
+      <c r="AM77" s="37">
         <f>IF(AJ77="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ77,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN77">
+      <c r="AN77" s="37">
         <f>IF(AJ77="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ77,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -12016,14 +12027,14 @@
       <c r="AG78" s="60" t="n"/>
       <c r="AH78" s="60" t="n"/>
       <c r="AI78" s="52" t="n"/>
-      <c r="AJ78" t="inlineStr"/>
-      <c r="AK78" t="inlineStr"/>
-      <c r="AL78" t="inlineStr"/>
-      <c r="AM78">
+      <c r="AJ78" s="37" t="inlineStr"/>
+      <c r="AK78" s="37" t="inlineStr"/>
+      <c r="AL78" s="37" t="inlineStr"/>
+      <c r="AM78" s="37">
         <f>IF(AJ78="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ78,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN78">
+      <c r="AN78" s="37">
         <f>IF(AJ78="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ78,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -12149,14 +12160,14 @@
       <c r="AG79" s="60" t="n"/>
       <c r="AH79" s="60" t="n"/>
       <c r="AI79" s="52" t="n"/>
-      <c r="AJ79" t="inlineStr"/>
-      <c r="AK79" t="inlineStr"/>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79">
+      <c r="AJ79" s="37" t="inlineStr"/>
+      <c r="AK79" s="37" t="inlineStr"/>
+      <c r="AL79" s="37" t="inlineStr"/>
+      <c r="AM79" s="37">
         <f>IF(AJ79="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ79,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN79">
+      <c r="AN79" s="37">
         <f>IF(AJ79="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ79,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -12286,14 +12297,14 @@
       <c r="AG80" s="60" t="n"/>
       <c r="AH80" s="60" t="n"/>
       <c r="AI80" s="52" t="n"/>
-      <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80">
+      <c r="AJ80" s="37" t="inlineStr"/>
+      <c r="AK80" s="37" t="inlineStr"/>
+      <c r="AL80" s="37" t="inlineStr"/>
+      <c r="AM80" s="37">
         <f>IF(AJ80="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ80,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN80">
+      <c r="AN80" s="37">
         <f>IF(AJ80="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ80,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -12425,14 +12436,14 @@
       <c r="AG81" s="60" t="n"/>
       <c r="AH81" s="60" t="n"/>
       <c r="AI81" s="52" t="n"/>
-      <c r="AJ81" t="inlineStr"/>
-      <c r="AK81" t="inlineStr"/>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81">
+      <c r="AJ81" s="37" t="inlineStr"/>
+      <c r="AK81" s="37" t="inlineStr"/>
+      <c r="AL81" s="37" t="inlineStr"/>
+      <c r="AM81" s="37">
         <f>IF(AJ81="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ81,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN81">
+      <c r="AN81" s="37">
         <f>IF(AJ81="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ81,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -12564,14 +12575,14 @@
       <c r="AG82" s="60" t="n"/>
       <c r="AH82" s="60" t="n"/>
       <c r="AI82" s="52" t="n"/>
-      <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="inlineStr"/>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82">
+      <c r="AJ82" s="37" t="inlineStr"/>
+      <c r="AK82" s="37" t="inlineStr"/>
+      <c r="AL82" s="37" t="inlineStr"/>
+      <c r="AM82" s="37">
         <f>IF(AJ82="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ82,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN82">
+      <c r="AN82" s="37">
         <f>IF(AJ82="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ82,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -12699,14 +12710,14 @@
       <c r="AG83" s="60" t="n"/>
       <c r="AH83" s="60" t="n"/>
       <c r="AI83" s="52" t="n"/>
-      <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="inlineStr"/>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83">
+      <c r="AJ83" s="37" t="inlineStr"/>
+      <c r="AK83" s="37" t="inlineStr"/>
+      <c r="AL83" s="37" t="inlineStr"/>
+      <c r="AM83" s="37">
         <f>IF(AJ83="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ83,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN83">
+      <c r="AN83" s="37">
         <f>IF(AJ83="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ83,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -12842,14 +12853,14 @@
       <c r="AG84" s="60" t="n"/>
       <c r="AH84" s="60" t="n"/>
       <c r="AI84" s="52" t="n"/>
-      <c r="AJ84" t="inlineStr"/>
-      <c r="AK84" t="inlineStr"/>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84">
+      <c r="AJ84" s="37" t="inlineStr"/>
+      <c r="AK84" s="37" t="inlineStr"/>
+      <c r="AL84" s="37" t="inlineStr"/>
+      <c r="AM84" s="37">
         <f>IF(AJ84="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ84,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN84">
+      <c r="AN84" s="37">
         <f>IF(AJ84="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ84,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -12991,14 +13002,14 @@
       <c r="AG85" s="60" t="n"/>
       <c r="AH85" s="60" t="n"/>
       <c r="AI85" s="52" t="n"/>
-      <c r="AJ85" t="inlineStr"/>
-      <c r="AK85" t="inlineStr"/>
-      <c r="AL85" t="inlineStr"/>
-      <c r="AM85">
+      <c r="AJ85" s="37" t="inlineStr"/>
+      <c r="AK85" s="37" t="inlineStr"/>
+      <c r="AL85" s="37" t="inlineStr"/>
+      <c r="AM85" s="37">
         <f>IF(AJ85="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ85,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN85">
+      <c r="AN85" s="37">
         <f>IF(AJ85="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ85,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -13128,14 +13139,14 @@
       <c r="AG86" s="60" t="n"/>
       <c r="AH86" s="60" t="n"/>
       <c r="AI86" s="52" t="n"/>
-      <c r="AJ86" t="inlineStr"/>
-      <c r="AK86" t="inlineStr"/>
-      <c r="AL86" t="inlineStr"/>
-      <c r="AM86">
+      <c r="AJ86" s="37" t="inlineStr"/>
+      <c r="AK86" s="37" t="inlineStr"/>
+      <c r="AL86" s="37" t="inlineStr"/>
+      <c r="AM86" s="37">
         <f>IF(AJ86="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ86,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN86">
+      <c r="AN86" s="37">
         <f>IF(AJ86="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ86,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -13267,14 +13278,14 @@
       <c r="AG87" s="60" t="n"/>
       <c r="AH87" s="60" t="n"/>
       <c r="AI87" s="52" t="n"/>
-      <c r="AJ87" t="inlineStr"/>
-      <c r="AK87" t="inlineStr"/>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87">
+      <c r="AJ87" s="37" t="inlineStr"/>
+      <c r="AK87" s="37" t="inlineStr"/>
+      <c r="AL87" s="37" t="inlineStr"/>
+      <c r="AM87" s="37">
         <f>IF(AJ87="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ87,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN87">
+      <c r="AN87" s="37">
         <f>IF(AJ87="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ87,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -13400,14 +13411,14 @@
       <c r="AG88" s="60" t="n"/>
       <c r="AH88" s="60" t="n"/>
       <c r="AI88" s="52" t="n"/>
-      <c r="AJ88" t="inlineStr"/>
-      <c r="AK88" t="inlineStr"/>
-      <c r="AL88" t="inlineStr"/>
-      <c r="AM88">
+      <c r="AJ88" s="37" t="inlineStr"/>
+      <c r="AK88" s="37" t="inlineStr"/>
+      <c r="AL88" s="37" t="inlineStr"/>
+      <c r="AM88" s="37">
         <f>IF(AJ88="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ88,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN88">
+      <c r="AN88" s="37">
         <f>IF(AJ88="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ88,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -13539,14 +13550,14 @@
       <c r="AG89" s="60" t="n"/>
       <c r="AH89" s="60" t="n"/>
       <c r="AI89" s="52" t="n"/>
-      <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89">
+      <c r="AJ89" s="37" t="inlineStr"/>
+      <c r="AK89" s="37" t="inlineStr"/>
+      <c r="AL89" s="37" t="inlineStr"/>
+      <c r="AM89" s="37">
         <f>IF(AJ89="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ89,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN89">
+      <c r="AN89" s="37">
         <f>IF(AJ89="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ89,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -13674,14 +13685,14 @@
       <c r="AG90" s="60" t="n"/>
       <c r="AH90" s="60" t="n"/>
       <c r="AI90" s="52" t="n"/>
-      <c r="AJ90" t="inlineStr"/>
-      <c r="AK90" t="inlineStr"/>
-      <c r="AL90" t="inlineStr"/>
-      <c r="AM90">
+      <c r="AJ90" s="37" t="inlineStr"/>
+      <c r="AK90" s="37" t="inlineStr"/>
+      <c r="AL90" s="37" t="inlineStr"/>
+      <c r="AM90" s="37">
         <f>IF(AJ90="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ90,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN90">
+      <c r="AN90" s="37">
         <f>IF(AJ90="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ90,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -13811,14 +13822,14 @@
       <c r="AG91" s="60" t="n"/>
       <c r="AH91" s="60" t="n"/>
       <c r="AI91" s="52" t="n"/>
-      <c r="AJ91" t="inlineStr"/>
-      <c r="AK91" t="inlineStr"/>
-      <c r="AL91" t="inlineStr"/>
-      <c r="AM91">
+      <c r="AJ91" s="37" t="inlineStr"/>
+      <c r="AK91" s="37" t="inlineStr"/>
+      <c r="AL91" s="37" t="inlineStr"/>
+      <c r="AM91" s="37">
         <f>IF(AJ91="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ91,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN91">
+      <c r="AN91" s="37">
         <f>IF(AJ91="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ91,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -13950,14 +13961,14 @@
       <c r="AG92" s="60" t="n"/>
       <c r="AH92" s="60" t="n"/>
       <c r="AI92" s="52" t="n"/>
-      <c r="AJ92" t="inlineStr"/>
-      <c r="AK92" t="inlineStr"/>
-      <c r="AL92" t="inlineStr"/>
-      <c r="AM92">
+      <c r="AJ92" s="37" t="inlineStr"/>
+      <c r="AK92" s="37" t="inlineStr"/>
+      <c r="AL92" s="37" t="inlineStr"/>
+      <c r="AM92" s="37">
         <f>IF(AJ92="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ92,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN92">
+      <c r="AN92" s="37">
         <f>IF(AJ92="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ92,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -14087,14 +14098,14 @@
       <c r="AG93" s="60" t="n"/>
       <c r="AH93" s="60" t="n"/>
       <c r="AI93" s="52" t="n"/>
-      <c r="AJ93" t="inlineStr"/>
-      <c r="AK93" t="inlineStr"/>
-      <c r="AL93" t="inlineStr"/>
-      <c r="AM93">
+      <c r="AJ93" s="37" t="inlineStr"/>
+      <c r="AK93" s="37" t="inlineStr"/>
+      <c r="AL93" s="37" t="inlineStr"/>
+      <c r="AM93" s="37">
         <f>IF(AJ93="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ93,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN93">
+      <c r="AN93" s="37">
         <f>IF(AJ93="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ93,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -14224,14 +14235,14 @@
       <c r="AG94" s="60" t="n"/>
       <c r="AH94" s="60" t="n"/>
       <c r="AI94" s="52" t="n"/>
-      <c r="AJ94" t="inlineStr"/>
-      <c r="AK94" t="inlineStr"/>
-      <c r="AL94" t="inlineStr"/>
-      <c r="AM94">
+      <c r="AJ94" s="37" t="inlineStr"/>
+      <c r="AK94" s="37" t="inlineStr"/>
+      <c r="AL94" s="37" t="inlineStr"/>
+      <c r="AM94" s="37">
         <f>IF(AJ94="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ94,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN94">
+      <c r="AN94" s="37">
         <f>IF(AJ94="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ94,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -14363,14 +14374,14 @@
       <c r="AG95" s="60" t="n"/>
       <c r="AH95" s="60" t="n"/>
       <c r="AI95" s="52" t="n"/>
-      <c r="AJ95" t="inlineStr"/>
-      <c r="AK95" t="inlineStr"/>
-      <c r="AL95" t="inlineStr"/>
-      <c r="AM95">
+      <c r="AJ95" s="37" t="inlineStr"/>
+      <c r="AK95" s="37" t="inlineStr"/>
+      <c r="AL95" s="37" t="inlineStr"/>
+      <c r="AM95" s="37">
         <f>IF(AJ95="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ95,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN95">
+      <c r="AN95" s="37">
         <f>IF(AJ95="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ95,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -14502,14 +14513,14 @@
       <c r="AG96" s="60" t="n"/>
       <c r="AH96" s="60" t="n"/>
       <c r="AI96" s="52" t="n"/>
-      <c r="AJ96" t="inlineStr"/>
-      <c r="AK96" t="inlineStr"/>
-      <c r="AL96" t="inlineStr"/>
-      <c r="AM96">
+      <c r="AJ96" s="37" t="inlineStr"/>
+      <c r="AK96" s="37" t="inlineStr"/>
+      <c r="AL96" s="37" t="inlineStr"/>
+      <c r="AM96" s="37">
         <f>IF(AJ96="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ96,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN96">
+      <c r="AN96" s="37">
         <f>IF(AJ96="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ96,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -14637,14 +14648,14 @@
       <c r="AG97" s="60" t="n"/>
       <c r="AH97" s="60" t="n"/>
       <c r="AI97" s="52" t="n"/>
-      <c r="AJ97" t="inlineStr"/>
-      <c r="AK97" t="inlineStr"/>
-      <c r="AL97" t="inlineStr"/>
-      <c r="AM97">
+      <c r="AJ97" s="37" t="inlineStr"/>
+      <c r="AK97" s="37" t="inlineStr"/>
+      <c r="AL97" s="37" t="inlineStr"/>
+      <c r="AM97" s="37">
         <f>IF(AJ97="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ97,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN97">
+      <c r="AN97" s="37">
         <f>IF(AJ97="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ97,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -14774,14 +14785,14 @@
       <c r="AG98" s="60" t="n"/>
       <c r="AH98" s="60" t="n"/>
       <c r="AI98" s="52" t="n"/>
-      <c r="AJ98" t="inlineStr"/>
-      <c r="AK98" t="inlineStr"/>
-      <c r="AL98" t="inlineStr"/>
-      <c r="AM98">
+      <c r="AJ98" s="37" t="inlineStr"/>
+      <c r="AK98" s="37" t="inlineStr"/>
+      <c r="AL98" s="37" t="inlineStr"/>
+      <c r="AM98" s="37">
         <f>IF(AJ98="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ98,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN98">
+      <c r="AN98" s="37">
         <f>IF(AJ98="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ98,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -14909,14 +14920,14 @@
       <c r="AG99" s="60" t="n"/>
       <c r="AH99" s="60" t="n"/>
       <c r="AI99" s="52" t="n"/>
-      <c r="AJ99" t="inlineStr"/>
-      <c r="AK99" t="inlineStr"/>
-      <c r="AL99" t="inlineStr"/>
-      <c r="AM99">
+      <c r="AJ99" s="37" t="inlineStr"/>
+      <c r="AK99" s="37" t="inlineStr"/>
+      <c r="AL99" s="37" t="inlineStr"/>
+      <c r="AM99" s="37">
         <f>IF(AJ99="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ99,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN99">
+      <c r="AN99" s="37">
         <f>IF(AJ99="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ99,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -15050,14 +15061,14 @@
       <c r="AG100" s="60" t="n"/>
       <c r="AH100" s="60" t="n"/>
       <c r="AI100" s="52" t="n"/>
-      <c r="AJ100" t="inlineStr"/>
-      <c r="AK100" t="inlineStr"/>
-      <c r="AL100" t="inlineStr"/>
-      <c r="AM100">
+      <c r="AJ100" s="37" t="inlineStr"/>
+      <c r="AK100" s="37" t="inlineStr"/>
+      <c r="AL100" s="37" t="inlineStr"/>
+      <c r="AM100" s="37">
         <f>IF(AJ100="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ100,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN100">
+      <c r="AN100" s="37">
         <f>IF(AJ100="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ100,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -15189,14 +15200,14 @@
       <c r="AG101" s="60" t="n"/>
       <c r="AH101" s="60" t="n"/>
       <c r="AI101" s="52" t="n"/>
-      <c r="AJ101" t="inlineStr"/>
-      <c r="AK101" t="inlineStr"/>
-      <c r="AL101" t="inlineStr"/>
-      <c r="AM101">
+      <c r="AJ101" s="37" t="inlineStr"/>
+      <c r="AK101" s="37" t="inlineStr"/>
+      <c r="AL101" s="37" t="inlineStr"/>
+      <c r="AM101" s="37">
         <f>IF(AJ101="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ101,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN101">
+      <c r="AN101" s="37">
         <f>IF(AJ101="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ101,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -15324,14 +15335,14 @@
       <c r="AG102" s="60" t="n"/>
       <c r="AH102" s="60" t="n"/>
       <c r="AI102" s="52" t="n"/>
-      <c r="AJ102" t="inlineStr"/>
-      <c r="AK102" t="inlineStr"/>
-      <c r="AL102" t="inlineStr"/>
-      <c r="AM102">
+      <c r="AJ102" s="37" t="inlineStr"/>
+      <c r="AK102" s="37" t="inlineStr"/>
+      <c r="AL102" s="37" t="inlineStr"/>
+      <c r="AM102" s="37">
         <f>IF(AJ102="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ102,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN102">
+      <c r="AN102" s="37">
         <f>IF(AJ102="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ102,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -15461,14 +15472,14 @@
       <c r="AG103" s="60" t="n"/>
       <c r="AH103" s="60" t="n"/>
       <c r="AI103" s="52" t="n"/>
-      <c r="AJ103" t="inlineStr"/>
-      <c r="AK103" t="inlineStr"/>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103">
+      <c r="AJ103" s="37" t="inlineStr"/>
+      <c r="AK103" s="37" t="inlineStr"/>
+      <c r="AL103" s="37" t="inlineStr"/>
+      <c r="AM103" s="37">
         <f>IF(AJ103="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ103,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN103">
+      <c r="AN103" s="37">
         <f>IF(AJ103="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ103,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -15600,14 +15611,14 @@
       <c r="AG104" s="60" t="n"/>
       <c r="AH104" s="60" t="n"/>
       <c r="AI104" s="52" t="n"/>
-      <c r="AJ104" t="inlineStr"/>
-      <c r="AK104" t="inlineStr"/>
-      <c r="AL104" t="inlineStr"/>
-      <c r="AM104">
+      <c r="AJ104" s="37" t="inlineStr"/>
+      <c r="AK104" s="37" t="inlineStr"/>
+      <c r="AL104" s="37" t="inlineStr"/>
+      <c r="AM104" s="37">
         <f>IF(AJ104="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ104,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN104">
+      <c r="AN104" s="37">
         <f>IF(AJ104="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ104,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -15739,14 +15750,14 @@
       <c r="AG105" s="60" t="n"/>
       <c r="AH105" s="60" t="n"/>
       <c r="AI105" s="52" t="n"/>
-      <c r="AJ105" t="inlineStr"/>
-      <c r="AK105" t="inlineStr"/>
-      <c r="AL105" t="inlineStr"/>
-      <c r="AM105">
+      <c r="AJ105" s="37" t="inlineStr"/>
+      <c r="AK105" s="37" t="inlineStr"/>
+      <c r="AL105" s="37" t="inlineStr"/>
+      <c r="AM105" s="37">
         <f>IF(AJ105="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ105,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN105">
+      <c r="AN105" s="37">
         <f>IF(AJ105="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ105,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -15888,14 +15899,14 @@
       <c r="AG106" s="60" t="n"/>
       <c r="AH106" s="60" t="n"/>
       <c r="AI106" s="52" t="n"/>
-      <c r="AJ106" t="inlineStr"/>
-      <c r="AK106" t="inlineStr"/>
-      <c r="AL106" t="inlineStr"/>
-      <c r="AM106">
+      <c r="AJ106" s="37" t="inlineStr"/>
+      <c r="AK106" s="37" t="inlineStr"/>
+      <c r="AL106" s="37" t="inlineStr"/>
+      <c r="AM106" s="37">
         <f>IF(AJ106="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ106,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
-      <c r="AN106">
+      <c r="AN106" s="37">
         <f>IF(AJ106="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ106,"проходить","НЕ проходить за ЄВВ"))</f>
         <v/>
       </c>
@@ -16862,4 +16873,1360 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B140"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="38" min="1" max="1"/>
+    <col width="10" customWidth="1" style="38" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="76" t="inlineStr">
+        <is>
+          <t>ФАКТИЧНИЙ РОЗПОДІЛ ДЕРЖЗАМОВЛЕННЯ В АСПІРАНТУРУ, 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Джерело: Додаток 2 до протоколу № 1 засідання конкурсної комісії МОН (mon.gov.ua), знімок archive.org від 27.04.2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ЦЕ ЄДИНИЙ РІК, за який вдалося дістати розподіл ПО ВИШАХ. Аналогічні документи за 2022, 2023 і 2025 у відкритому доступі не знайдено.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>УВАГА: 2024 рахувався за СТАРИМ класифікатором (галузі 12, 14, 17) і БЕЗ формули — рішення ухвалювались вручну.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Формульний розподіл діє лише з 2025 (наказ МОН № 863 від 17.06.2025), тому 2024 — орієнтир про масштаб, а не прогноз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="77" t="inlineStr">
+        <is>
+          <t>ЗАПОРІЗЬКА ПОЛІТЕХНІКА — усе, що отримала у 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="78" t="inlineStr">
+        <is>
+          <t>Галузь</t>
+        </is>
+      </c>
+      <c r="B8" s="78" t="inlineStr">
+        <is>
+          <t>Місць</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>13 Механічна інженерія</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14 Електрична інженерія</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12 Інформаційні технології</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>05 Соціальні та поведінкові науки</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07 Управління та адміністрування</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>19 Архітектора та будівництво</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>08 Право</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>23 Соціальна робота</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="77" t="inlineStr">
+        <is>
+          <t>РАЗОМ по вишу</t>
+        </is>
+      </c>
+      <c r="B17" s="77" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="77" t="inlineStr">
+        <is>
+          <t>Галузь 17 «Електроніка, автоматизація та електронні комунікації» — 0 місць, вишу в переліку НЕМАЄ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="77" t="inlineStr">
+        <is>
+          <t>ГАЛУЗЬ 12 ІНФОРМАЦІЙНІ ТЕХНОЛОГІЇ — усього 619 місць, 56 ЗВО</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="78" t="inlineStr">
+        <is>
+          <t>ЗВО</t>
+        </is>
+      </c>
+      <c r="B21" s="78" t="inlineStr">
+        <is>
+          <t>Місць</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Харківський національний університет радіоелектроніки</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Національний технічний університет України «Київський політехнічний інститут імені Ігоря Сікорського»</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Національний університет «Львівська політехніка»</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Київський національний університет імені Тараса Шевченка</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Національний технічний університет «Харківський політехнічний інститут»</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Національний авіаційний університет</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Державний університет інформаційно-комунікаційних технологій</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Вінницький національний технічний університет</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Львівський національний університет імені Івана Франка</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Національний аерокосмічний університет ім. М. Є. Жуковського «Харківський авіаційний інститут»</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Національний університет «Одеська політехніка»</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Національний університет біоресурсів і природокористування України</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Національний технічний університет «Дніпровська політехніка»</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Сумський державний університет</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Черкаський державний технологічний університет</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Державний торговельно-економічний університет</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Західноукраїнський національний університет</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Тернопільський національний технічний університет імені Івана Пулюя</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Харківський національний університет імені В.Н. Каразіна</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Дніпровський національний університет імені Олеся Гончара</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Хмельницький національний університет</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Національний університет «Києво-Могилянська академія»</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Державний університет «Житомирська політехніка»</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Національний університет «Запорізька політехніка»</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Український державний університет науки і технологій</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Державний вищий навчальний заклад «Ужгородський національний університет»</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Національний університет водного господарства та природокористування</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Національний університет кораблебудування імені адмірала Макарова</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Одеський національний університет імені І. І. Мечникова</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16 Херсонський національний технічний університет</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Запорізький національний університет</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Київський національний університет будівництва і архітектури</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Луцький національний технічний університет</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Національний транспортний університет</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Національний університет «Чернігівська політехніка»</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Харківський національний економічний університет імені Семена Кузнеця</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Державний університет інтелектуальних технологій і зв'язку</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>15 Міжнародний гуманітарний університет</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Національний університет «Одеська юридична академія»</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Харківський національний університет міського господарства імені О.М. Бекетова</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Державний вищий навчальний заклад «Донецький національний технічний університет»</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Державний університет інфраструктури та технологій</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Житомирський державний університет імені Івана Франка</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Київський національний університет технологій та дизайну</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Кременчуцький національний університет імені Михайла Остроградського</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Національний лісотехнічний університет України</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Національний університет «Полтавська політехніка імені Юрія Кондратюка»</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Національний університет харчових технологій</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Одеський національний морський університет</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Приватна установа «Університет «Київська школа економіки»</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Східноукраїнський національний університет імені Володимира Даля</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Український державний університет залізничного транспорту</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Харківський національний автомобільно-дорожній університет</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Херсонський державний університет</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Черкаський національний університет імені Богдана Хмельницького</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Чорноморський національний університет імені Петра Могили</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="77" t="inlineStr">
+        <is>
+          <t>ГАЛУЗЬ 17 ЕЛЕКТРОНІКА, АВТОМАТИЗАЦІЯ ТА ЕЛЕКТРОННІ КОМУНІКАЦІЇ — усього 259 місць, 30 ЗВО</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="78" t="inlineStr">
+        <is>
+          <t>ЗВО</t>
+        </is>
+      </c>
+      <c r="B80" s="78" t="inlineStr">
+        <is>
+          <t>Місць</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Національний технічний університет України «Київський політехнічний інститут імені Ігоря Сікорського»</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Національний університет «Львівська політехніка»</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Харківський національний університет радіоелектроніки</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Національний технічний університет «Харківський політехнічний інститут»</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Національний авіаційний університет</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Національний аерокосмічний університет ім. М. Є. Жуковського «Харківський авіаційний інститут»</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Івано-Франківський національний технічний університет нафти і газу</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Вінницький національний технічний університет</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Державний університет інформаційно-комунікаційних технологій</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Національний університет «Одеська політехніка»</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Державний університет інтелектуальних технологій і зв'язку</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Київський національний університет імені Тараса Шевченка</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Національний технічний університет «Дніпровська політехніка»</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Державний університет «Житомирська політехніка»</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Дніпровський національний університет імені Олеся Гончара</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Донбаська державна машинобудівна академія</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Кременчуцький національний університет імені Михайла Остроградського</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Криворізький національний університет</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Національний університет біоресурсів і природокористування України</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Національний університет кораблебудування імені адмірала Макарова</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Національний університет харчових технологій</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Одеський національний технологічний університет</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Прикарпатський національний університет імені Василя Стефаника</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Тернопільський національний технічний університет імені Івана Пулюя</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Український державний університет залізничного транспорту</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Харківський національний університет імені В.Н. Каразіна</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Херсонська державна морська академія</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Центральноукраїнський національний технічний університет</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Черкаський державний технологічний університет</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Чернівецький національний університет імені Юрія Федьковича</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="77" t="inlineStr">
+        <is>
+          <t>ГАЛУЗЬ 14 ЕЛЕКТРИЧНА ІНЖЕНЕРІЯ — усього 226 місць, 27 ЗВО</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="78" t="inlineStr">
+        <is>
+          <t>ЗВО</t>
+        </is>
+      </c>
+      <c r="B113" s="78" t="inlineStr">
+        <is>
+          <t>Місць</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Національний технічний університет України «Київський політехнічний інститут імені Ігоря Сікорського»</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>18 Національний технічний університет «Харківський політехнічний інститут»</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Національний університет кораблебудування імені адмірала Макарова</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Національний університет «Львівська політехніка»</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Національний університет біоресурсів і природокористування України</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Національний університет «Одеська політехніка»</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Національний університет «Запорізька політехніка»</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Національний авіаційний університет</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Одеський національний технологічний університет</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Вінницький національний технічний університет</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Національний аерокосмічний університет ім. М. Є. Жуковського «Харківський авіаційний інститут»</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Національний університет харчових технологій</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Харківський національний університет міського господарства імені О.М. Бекетова</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Державний біотехнологічний університет</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Кременчуцький національний університет імені Михайла Остроградського</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Криворізький національний університет</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Національний технічний університет «Дніпровська політехніка»</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Тернопільський національний технічний університет імені Івана Пулюя</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Український державний університет науки і технологій</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Державний вищий навчальний заклад «Приазовський державний технічний університет»</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Дніпровський державний технічний університет</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Запорізький національний університет</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Київський національний університет будівництва і архітектури</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Київський національний університет технологій та дизайну</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Національний транспортний університет</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Національний університет «Чернігівська політехніка»</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Таврійський державний агротехнологічний університет імені Дмитра Моторного</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/aspirantura_kalkulyator.xlsx
+++ b/aspirantura_kalkulyator.xlsx
@@ -466,9 +466,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -15911,6 +15909,144 @@
         <v/>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>G3 Електрична інженерія</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Національний університет "Запорізька політехніка"</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Запоріжжя</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Запорізька</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ТАК</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Фіксована</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ні</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>електроенергетика, електротехніка та електромеханіка</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>26</v>
+      </c>
+      <c r="M107">
+        <f>IF(K107=0,"н/д",L107/K107)</f>
+        <v/>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>27.08.2026 (скриншот сторінки пропозиції, кампанія 2026)</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>не встановлено</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T107">
+        <f>0.2*'Бали кандидатів'!$B$6+0.2*'Бали кандидатів'!$B$7+O107*'Бали кандидатів'!$B$9+P107*'Бали кандидатів'!$B$10+Q107*'Бали кандидатів'!$B$11</f>
+        <v/>
+      </c>
+      <c r="U107">
+        <f>0.2*'Бали кандидатів'!$C$6+0.2*'Бали кандидатів'!$C$7+O107*'Бали кандидатів'!$C$9+P107*'Бали кандидатів'!$C$10+Q107*'Бали кандидатів'!$C$11</f>
+        <v/>
+      </c>
+      <c r="V107">
+        <f>IF('Бали кандидатів'!$B$14&gt;=300,"OK","НЕ ДОПУЩЕНО")</f>
+        <v/>
+      </c>
+      <c r="W107">
+        <f>IF('Бали кандидатів'!$C$14&gt;=300,"OK","НЕ ДОПУЩЕНО")</f>
+        <v/>
+      </c>
+      <c r="X107">
+        <f>IF(AND(OR(R107="—",'Бали кандидатів'!$B$9&gt;=R107),OR(S107="—",'Бали кандидатів'!$B$10&gt;=S107)),"проходить","НИЖЧЕ мін. балу")</f>
+        <v/>
+      </c>
+      <c r="Y107">
+        <f>IF(AND(OR(R107="—",'Бали кандидатів'!$C$9&gt;=R107),OR(S107="—",'Бали кандидатів'!$C$10&gt;=S107)),"проходить","НИЖЧЕ мін. балу")</f>
+        <v/>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>Тільки іспит зі спеціальності</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>ГАЛУЗЬ «Інженерія, виробництво та будівництво», НЕ IT. Ліцензований обсяг = 0, тому «заяв на місце» не рахується. Мін. бал за іноземну та ТЗНК на сторінці НЕ вказано (на відміну від пропозицій F3, де скрізь 150). Вартість контракту 48500 грн/рік. Подача 07.08–07.09.2026, навчання 01.10.2026–30.09.2030.</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>https://vstup.osvita.ua/r9/91/entrance.html</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>https://vstup.osvita.ua/r9/91/</t>
+        </is>
+      </c>
+      <c r="AJ107" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107">
+        <f>IF(AJ107="","дані ще не вивантажені",IF('Бали кандидатів'!$B$7&gt;=AJ107,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+      <c r="AN107">
+        <f>IF(AJ107="","дані ще не вивантажені",IF('Бали кандидатів'!$C$7&gt;=AJ107,"проходить","НЕ проходить за ЄВВ"))</f>
+        <v/>
+      </c>
+    </row>
     <row r="108" ht="15" customHeight="1" s="38">
       <c r="A108" s="45" t="inlineStr">
         <is>
@@ -16889,35 +17025,35 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>ФАКТИЧНИЙ РОЗПОДІЛ ДЕРЖЗАМОВЛЕННЯ В АСПІРАНТУРУ, 2024</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Джерело: Додаток 2 до протоколу № 1 засідання конкурсної комісії МОН (mon.gov.ua), знімок archive.org від 27.04.2025.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>ЦЕ ЄДИНИЙ РІК, за який вдалося дістати розподіл ПО ВИШАХ. Аналогічні документи за 2022, 2023 і 2025 у відкритому доступі не знайдено.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>УВАГА: 2024 рахувався за СТАРИМ класифікатором (галузі 12, 14, 17) і БЕЗ формули — рішення ухвалювались вручну.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Формульний розподіл діє лише з 2025 (наказ МОН № 863 від 17.06.2025), тому 2024 — орієнтир про масштаб, а не прогноз.</t>
         </is>
@@ -16943,82 +17079,82 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>13 Механічна інженерія</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="37" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>14 Електрична інженерія</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="37" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>12 Інформаційні технології</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>05 Соціальні та поведінкові науки</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>07 Управління та адміністрування</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>19 Архітектора та будівництво</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>08 Право</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>23 Соціальна робота</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17059,562 +17195,562 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Харківський національний університет радіоелектроніки</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="37" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>Національний технічний університет України «Київський політехнічний інститут імені Ігоря Сікорського»</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="37" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Львівська політехніка»</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="37" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>Київський національний університет імені Тараса Шевченка</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="37" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>Національний технічний університет «Харківський політехнічний інститут»</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="37" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>Національний авіаційний університет</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="37" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>Державний університет інформаційно-комунікаційних технологій</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="37" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>Вінницький національний технічний університет</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="37" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>Львівський національний університет імені Івана Франка</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="37" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>Національний аерокосмічний університет ім. М. Є. Жуковського «Харківський авіаційний інститут»</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="37" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Одеська політехніка»</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="37" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>Національний університет біоресурсів і природокористування України</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="37" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>Національний технічний університет «Дніпровська політехніка»</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="37" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>Сумський державний університет</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="37" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>Черкаський державний технологічний університет</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="37" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>Державний торговельно-економічний університет</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="37" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>Західноукраїнський національний університет</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="37" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>Тернопільський національний технічний університет імені Івана Пулюя</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="37" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="37" t="inlineStr">
         <is>
           <t>Харківський національний університет імені В.Н. Каразіна</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="37" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>Дніпровський національний університет імені Олеся Гончара</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="37" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>Хмельницький національний університет</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="37" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Києво-Могилянська академія»</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="37" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="37" t="inlineStr">
         <is>
           <t>Державний університет «Житомирська політехніка»</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Запорізька політехніка»</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="37" t="inlineStr">
         <is>
           <t>Український державний університет науки і технологій</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="37" t="inlineStr">
         <is>
           <t>Державний вищий навчальний заклад «Ужгородський національний університет»</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="37" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="37" t="inlineStr">
         <is>
           <t>Національний університет водного господарства та природокористування</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="37" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>Національний університет кораблебудування імені адмірала Макарова</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="37" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="37" t="inlineStr">
         <is>
           <t>Одеський національний університет імені І. І. Мечникова</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="37" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="37" t="inlineStr">
         <is>
           <t>16 Херсонський національний технічний університет</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="37" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="37" t="inlineStr">
         <is>
           <t>Запорізький національний університет</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>Київський національний університет будівництва і архітектури</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>Луцький національний технічний університет</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>Національний транспортний університет</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Чернігівська політехніка»</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>Харківський національний економічний університет імені Семена Кузнеця</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>Державний університет інтелектуальних технологій і зв'язку</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>15 Міжнародний гуманітарний університет</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Одеська юридична академія»</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>Харківський національний університет міського господарства імені О.М. Бекетова</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="37" t="inlineStr">
         <is>
           <t>Державний вищий навчальний заклад «Донецький національний технічний університет»</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>Державний університет інфраструктури та технологій</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="37" t="inlineStr">
         <is>
           <t>Житомирський державний університет імені Івана Франка</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>Київський національний університет технологій та дизайну</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="37" t="inlineStr">
         <is>
           <t>Кременчуцький національний університет імені Михайла Остроградського</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>Національний лісотехнічний університет України</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Полтавська політехніка імені Юрія Кондратюка»</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="37" t="inlineStr">
         <is>
           <t>Національний університет харчових технологій</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="37" t="inlineStr">
         <is>
           <t>Одеський національний морський університет</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="37" t="inlineStr">
         <is>
           <t>Приватна установа «Університет «Київська школа економіки»</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="37" t="inlineStr">
         <is>
           <t>Східноукраїнський національний університет імені Володимира Даля</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>Український державний університет залізничного транспорту</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="37" t="inlineStr">
         <is>
           <t>Харківський національний автомобільно-дорожній університет</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="37" t="inlineStr">
         <is>
           <t>Херсонський державний університет</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="37" t="inlineStr">
         <is>
           <t>Черкаський національний університет імені Богдана Хмельницького</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="37" t="inlineStr">
         <is>
           <t>Чорноморський національний університет імені Петра Могили</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17638,302 +17774,302 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="37" t="inlineStr">
         <is>
           <t>Національний технічний університет України «Київський політехнічний інститут імені Ігоря Сікорського»</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="37" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Львівська політехніка»</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="37" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="37" t="inlineStr">
         <is>
           <t>Харківський національний університет радіоелектроніки</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="37" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="37" t="inlineStr">
         <is>
           <t>Національний технічний університет «Харківський політехнічний інститут»</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="37" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="37" t="inlineStr">
         <is>
           <t>Національний авіаційний університет</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="37" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="37" t="inlineStr">
         <is>
           <t>Національний аерокосмічний університет ім. М. Є. Жуковського «Харківський авіаційний інститут»</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="37" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="37" t="inlineStr">
         <is>
           <t>Івано-Франківський національний технічний університет нафти і газу</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="37" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="37" t="inlineStr">
         <is>
           <t>Вінницький національний технічний університет</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="37" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="37" t="inlineStr">
         <is>
           <t>Державний університет інформаційно-комунікаційних технологій</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="37" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Одеська політехніка»</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="37" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="37" t="inlineStr">
         <is>
           <t>Державний університет інтелектуальних технологій і зв'язку</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="37" t="inlineStr">
         <is>
           <t>Київський національний університет імені Тараса Шевченка</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="37" t="inlineStr">
         <is>
           <t>Національний технічний університет «Дніпровська політехніка»</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="37" t="inlineStr">
         <is>
           <t>Державний університет «Житомирська політехніка»</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="37" t="inlineStr">
         <is>
           <t>Дніпровський національний університет імені Олеся Гончара</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="37" t="inlineStr">
         <is>
           <t>Донбаська державна машинобудівна академія</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="37" t="inlineStr">
         <is>
           <t>Кременчуцький національний університет імені Михайла Остроградського</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="37" t="inlineStr">
         <is>
           <t>Криворізький національний університет</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="37" t="inlineStr">
         <is>
           <t>Національний університет біоресурсів і природокористування України</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="37" t="inlineStr">
         <is>
           <t>Національний університет кораблебудування імені адмірала Макарова</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="37" t="inlineStr">
         <is>
           <t>Національний університет харчових технологій</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="37" t="inlineStr">
         <is>
           <t>Одеський національний технологічний університет</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="37" t="inlineStr">
         <is>
           <t>Прикарпатський національний університет імені Василя Стефаника</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="37" t="inlineStr">
         <is>
           <t>Тернопільський національний технічний університет імені Івана Пулюя</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="37" t="inlineStr">
         <is>
           <t>Український державний університет залізничного транспорту</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="37" t="inlineStr">
         <is>
           <t>Харківський національний університет імені В.Н. Каразіна</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="37" t="inlineStr">
         <is>
           <t>Херсонська державна морська академія</t>
         </is>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="37" t="inlineStr">
         <is>
           <t>Центральноукраїнський національний технічний університет</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="37" t="inlineStr">
         <is>
           <t>Черкаський державний технологічний університет</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="37" t="inlineStr">
         <is>
           <t>Чернівецький національний університет імені Юрія Федьковича</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -17957,272 +18093,272 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="37" t="inlineStr">
         <is>
           <t>Національний технічний університет України «Київський політехнічний інститут імені Ігоря Сікорського»</t>
         </is>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="37" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="37" t="inlineStr">
         <is>
           <t>18 Національний технічний університет «Харківський політехнічний інститут»</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="37" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="37" t="inlineStr">
         <is>
           <t>Національний університет кораблебудування імені адмірала Макарова</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="37" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Львівська політехніка»</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="37" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="37" t="inlineStr">
         <is>
           <t>Національний університет біоресурсів і природокористування України</t>
         </is>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="37" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Одеська політехніка»</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="37" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Запорізька політехніка»</t>
         </is>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" s="37" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="37" t="inlineStr">
         <is>
           <t>Національний авіаційний університет</t>
         </is>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="37" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="37" t="inlineStr">
         <is>
           <t>Одеський національний технологічний університет</t>
         </is>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="37" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="37" t="inlineStr">
         <is>
           <t>Вінницький національний технічний університет</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="37" t="inlineStr">
         <is>
           <t>Національний аерокосмічний університет ім. М. Є. Жуковського «Харківський авіаційний інститут»</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="37" t="inlineStr">
         <is>
           <t>Національний університет харчових технологій</t>
         </is>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="37" t="inlineStr">
         <is>
           <t>Харківський національний університет міського господарства імені О.М. Бекетова</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="37" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="37" t="inlineStr">
         <is>
           <t>Державний біотехнологічний університет</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="37" t="inlineStr">
         <is>
           <t>Кременчуцький національний університет імені Михайла Остроградського</t>
         </is>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="37" t="inlineStr">
         <is>
           <t>Криворізький національний університет</t>
         </is>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="37" t="inlineStr">
         <is>
           <t>Національний технічний університет «Дніпровська політехніка»</t>
         </is>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="37" t="inlineStr">
         <is>
           <t>Тернопільський національний технічний університет імені Івана Пулюя</t>
         </is>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="37" t="inlineStr">
         <is>
           <t>Український державний університет науки і технологій</t>
         </is>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="37" t="inlineStr">
         <is>
           <t>Державний вищий навчальний заклад «Приазовський державний технічний університет»</t>
         </is>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="37" t="inlineStr">
         <is>
           <t>Дніпровський державний технічний університет</t>
         </is>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="37" t="inlineStr">
         <is>
           <t>Запорізький національний університет</t>
         </is>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="37" t="inlineStr">
         <is>
           <t>Київський національний університет будівництва і архітектури</t>
         </is>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="37" t="inlineStr">
         <is>
           <t>Київський національний університет технологій та дизайну</t>
         </is>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="37" t="inlineStr">
         <is>
           <t>Національний транспортний університет</t>
         </is>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="37" t="inlineStr">
         <is>
           <t>Національний університет «Чернігівська політехніка»</t>
         </is>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="37" t="inlineStr">
         <is>
           <t>Таврійський державний агротехнологічний університет імені Дмитра Моторного</t>
         </is>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" s="37" t="n">
         <v>3</v>
       </c>
     </row>
